--- a/tables_and_figures/input_tables/national_errors.xlsx
+++ b/tables_and_figures/input_tables/national_errors.xlsx
@@ -477,7 +477,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -545,7 +545,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -613,7 +613,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -681,7 +681,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -749,7 +749,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -817,7 +817,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -885,7 +885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -953,7 +953,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G15" t="b">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G16" t="b">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G17" t="b">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G18" t="b">
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18">
         <v>52.18745796266161</v>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G19" t="b">
@@ -1646,7 +1646,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19">
         <v>52.18745796266161</v>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G20" t="b">
@@ -1714,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20">
         <v>52.18745796266161</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G21" t="b">
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21">
         <v>52.18745796266161</v>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G22" t="b">
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22">
         <v>87.20709012470589</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G23" t="b">
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23">
         <v>87.20709012470589</v>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G24" t="b">
@@ -1986,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24">
         <v>87.20709012470589</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G25" t="b">
@@ -2054,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25">
         <v>87.20709012470589</v>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G26" t="b">
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26">
         <v>88.86751429572016</v>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G27" t="b">
@@ -2190,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27">
         <v>88.86751429572016</v>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G28" t="b">
@@ -2258,7 +2258,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28">
         <v>88.86751429572016</v>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G29" t="b">
@@ -2326,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29">
         <v>88.86751429572016</v>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G30" t="b">
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30">
         <v>86.23135014450705</v>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G31" t="b">
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31">
         <v>86.23135014450705</v>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G32" t="b">
@@ -2530,7 +2530,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32">
         <v>86.23135014450705</v>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G33" t="b">
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33">
         <v>86.23135014450705</v>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G34" t="b">
@@ -2666,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34">
         <v>62.08476673915369</v>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G35" t="b">
@@ -2734,7 +2734,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35">
         <v>62.08476673915369</v>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G36" t="b">
@@ -2802,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36">
         <v>62.08476673915369</v>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="G37" t="b">
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37">
         <v>62.08476673915369</v>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G378" t="b">
@@ -26058,7 +26058,7 @@
         <v>0</v>
       </c>
       <c r="J378" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K378">
         <v>57.1867220532585</v>
@@ -26113,7 +26113,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G379" t="b">
@@ -26126,7 +26126,7 @@
         <v>0</v>
       </c>
       <c r="J379" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K379">
         <v>57.1867220532585</v>
@@ -26181,7 +26181,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G380" t="b">
@@ -26194,7 +26194,7 @@
         <v>0</v>
       </c>
       <c r="J380" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K380">
         <v>57.1867220532585</v>
@@ -26249,7 +26249,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G381" t="b">
@@ -26262,7 +26262,7 @@
         <v>0</v>
       </c>
       <c r="J381" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K381">
         <v>57.1867220532585</v>

--- a/tables_and_figures/input_tables/national_errors.xlsx
+++ b/tables_and_figures/input_tables/national_errors.xlsx
@@ -615,7 +615,7 @@
         <v>15.48461548440772</v>
       </c>
       <c r="N2">
-        <v>20.97260097704803</v>
+        <v>20.97275263814991</v>
       </c>
       <c r="O2">
         <v>20.97276423076761</v>
@@ -671,7 +671,7 @@
         <v>15.48461548440772</v>
       </c>
       <c r="N3">
-        <v>20.97260097704803</v>
+        <v>20.97275263814991</v>
       </c>
       <c r="O3">
         <v>20.97276423076761</v>
@@ -727,7 +727,7 @@
         <v>15.48461548440772</v>
       </c>
       <c r="N4">
-        <v>20.97260097704803</v>
+        <v>20.97275263814991</v>
       </c>
       <c r="O4">
         <v>20.97276423076761</v>
@@ -739,7 +739,7 @@
         <v>26</v>
       </c>
       <c r="S4">
-        <v>-0.0001632537194151684</v>
+        <v>-1.159261753536089E-05</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -783,7 +783,7 @@
         <v>15.48461548440772</v>
       </c>
       <c r="N5">
-        <v>20.97260097704803</v>
+        <v>20.97275263814991</v>
       </c>
       <c r="O5">
         <v>20.97276423076761</v>
@@ -839,7 +839,7 @@
         <v>41.815548117088</v>
       </c>
       <c r="N6">
-        <v>32.26727352520333</v>
+        <v>32.26674623493708</v>
       </c>
       <c r="O6">
         <v>32.26672641913032</v>
@@ -895,7 +895,7 @@
         <v>41.815548117088</v>
       </c>
       <c r="N7">
-        <v>32.26727352520333</v>
+        <v>32.26674623493708</v>
       </c>
       <c r="O7">
         <v>32.26672641913032</v>
@@ -951,7 +951,7 @@
         <v>41.815548117088</v>
       </c>
       <c r="N8">
-        <v>32.26727352520333</v>
+        <v>32.26674623493708</v>
       </c>
       <c r="O8">
         <v>32.26672641913032</v>
@@ -963,7 +963,7 @@
         <v>26</v>
       </c>
       <c r="S8">
-        <v>0.0005471060727457733</v>
+        <v>1.981580650123327E-05</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1007,7 +1007,7 @@
         <v>41.815548117088</v>
       </c>
       <c r="N9">
-        <v>32.26727352520333</v>
+        <v>32.26674623493708</v>
       </c>
       <c r="O9">
         <v>32.26672641913032</v>
@@ -1063,7 +1063,7 @@
         <v>63.11253329112523</v>
       </c>
       <c r="N10">
-        <v>64.40752705028086</v>
+        <v>64.40774991932034</v>
       </c>
       <c r="O10">
         <v>64.40774340258896</v>
@@ -1119,7 +1119,7 @@
         <v>63.11253329112523</v>
       </c>
       <c r="N11">
-        <v>64.40752705028086</v>
+        <v>64.40774991932034</v>
       </c>
       <c r="O11">
         <v>64.40774340258896</v>
@@ -1175,7 +1175,7 @@
         <v>63.11253329112523</v>
       </c>
       <c r="N12">
-        <v>64.40752705028086</v>
+        <v>64.40774991932034</v>
       </c>
       <c r="O12">
         <v>64.40774340258896</v>
@@ -1187,7 +1187,7 @@
         <v>26</v>
       </c>
       <c r="S12">
-        <v>-0.0002163523078690943</v>
+        <v>6.516731620997973E-06</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -1231,7 +1231,7 @@
         <v>63.11253329112523</v>
       </c>
       <c r="N13">
-        <v>64.40752705028086</v>
+        <v>64.40774991932034</v>
       </c>
       <c r="O13">
         <v>64.40774340258896</v>
@@ -1287,7 +1287,7 @@
         <v>27.33559260610176</v>
       </c>
       <c r="N14">
-        <v>23.90892012698406</v>
+        <v>23.90892045602798</v>
       </c>
       <c r="O14">
         <v>23.90891074517564</v>
@@ -1343,7 +1343,7 @@
         <v>27.33559260610176</v>
       </c>
       <c r="N15">
-        <v>23.90892012698406</v>
+        <v>23.90892045602798</v>
       </c>
       <c r="O15">
         <v>23.90891074517564</v>
@@ -1399,7 +1399,7 @@
         <v>27.33559260610176</v>
       </c>
       <c r="N16">
-        <v>23.90892012698406</v>
+        <v>23.90892045602798</v>
       </c>
       <c r="O16">
         <v>23.90891074517564</v>
@@ -1411,7 +1411,7 @@
         <v>26</v>
       </c>
       <c r="S16">
-        <v>9.381808233066558E-06</v>
+        <v>9.710852147404303E-06</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -1455,7 +1455,7 @@
         <v>27.33559260610176</v>
       </c>
       <c r="N17">
-        <v>23.90892012698406</v>
+        <v>23.90892045602798</v>
       </c>
       <c r="O17">
         <v>23.90891074517564</v>
@@ -1490,13 +1490,13 @@
         <v>23</v>
       </c>
       <c r="G18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
@@ -1511,7 +1511,7 @@
         <v>52.00183281956703</v>
       </c>
       <c r="N18">
-        <v>52.18741682607639</v>
+        <v>54.59793107255933</v>
       </c>
       <c r="O18">
         <v>51.60214900749024</v>
@@ -1546,13 +1546,13 @@
         <v>23</v>
       </c>
       <c r="G19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
       </c>
       <c r="I19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
@@ -1567,7 +1567,7 @@
         <v>52.00183281956703</v>
       </c>
       <c r="N19">
-        <v>52.18741682607639</v>
+        <v>54.59793107255933</v>
       </c>
       <c r="O19">
         <v>51.60214900749024</v>
@@ -1602,13 +1602,13 @@
         <v>23</v>
       </c>
       <c r="G20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
       </c>
       <c r="I20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
@@ -1623,7 +1623,7 @@
         <v>52.00183281956703</v>
       </c>
       <c r="N20">
-        <v>52.18741682607639</v>
+        <v>54.59793107255933</v>
       </c>
       <c r="O20">
         <v>51.60214900749024</v>
@@ -1635,7 +1635,7 @@
         <v>26</v>
       </c>
       <c r="S20">
-        <v>-4.113658521598396E-05</v>
+        <v>2.410473109897715</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -1658,13 +1658,13 @@
         <v>23</v>
       </c>
       <c r="G21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
       </c>
       <c r="I21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
@@ -1679,7 +1679,7 @@
         <v>52.00183281956703</v>
       </c>
       <c r="N21">
-        <v>52.18741682607639</v>
+        <v>54.59793107255933</v>
       </c>
       <c r="O21">
         <v>51.60214900749024</v>
@@ -1735,7 +1735,7 @@
         <v>91.22110481989766</v>
       </c>
       <c r="N22">
-        <v>87.20732898923262</v>
+        <v>87.20709087735455</v>
       </c>
       <c r="O22">
         <v>91.84544467509298</v>
@@ -1791,7 +1791,7 @@
         <v>91.22110481989766</v>
       </c>
       <c r="N23">
-        <v>87.20732898923262</v>
+        <v>87.20709087735455</v>
       </c>
       <c r="O23">
         <v>91.84544467509298</v>
@@ -1847,7 +1847,7 @@
         <v>91.22110481989766</v>
       </c>
       <c r="N24">
-        <v>87.20732898923262</v>
+        <v>87.20709087735455</v>
       </c>
       <c r="O24">
         <v>91.84544467509298</v>
@@ -1859,7 +1859,7 @@
         <v>26</v>
       </c>
       <c r="S24">
-        <v>0.0002388645267359379</v>
+        <v>7.52648654511745E-07</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -1903,7 +1903,7 @@
         <v>91.22110481989766</v>
       </c>
       <c r="N25">
-        <v>87.20732898923262</v>
+        <v>87.20709087735455</v>
       </c>
       <c r="O25">
         <v>91.84544467509298</v>
@@ -1959,7 +1959,7 @@
         <v>84.27871221524576</v>
       </c>
       <c r="N26">
-        <v>88.86746088051697</v>
+        <v>88.86751029469819</v>
       </c>
       <c r="O26">
         <v>82.16730772435594</v>
@@ -2015,7 +2015,7 @@
         <v>84.27871221524576</v>
       </c>
       <c r="N27">
-        <v>88.86746088051697</v>
+        <v>88.86751029469819</v>
       </c>
       <c r="O27">
         <v>82.16730772435594</v>
@@ -2071,7 +2071,7 @@
         <v>84.27871221524576</v>
       </c>
       <c r="N28">
-        <v>88.86746088051697</v>
+        <v>88.86751029469819</v>
       </c>
       <c r="O28">
         <v>82.16730772435594</v>
@@ -2083,7 +2083,7 @@
         <v>26</v>
       </c>
       <c r="S28">
-        <v>-5.341520317170279E-05</v>
+        <v>-4.001021958188744E-06</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -2127,7 +2127,7 @@
         <v>84.27871221524576</v>
       </c>
       <c r="N29">
-        <v>88.86746088051697</v>
+        <v>88.86751029469819</v>
       </c>
       <c r="O29">
         <v>82.16730772435594</v>
@@ -2162,13 +2162,13 @@
         <v>23</v>
       </c>
       <c r="G30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
       </c>
       <c r="I30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
@@ -2183,7 +2183,7 @@
         <v>83.08196421090184</v>
       </c>
       <c r="N30">
-        <v>86.23129934518856</v>
+        <v>81.09639830618195</v>
       </c>
       <c r="O30">
         <v>81.32343450062355</v>
@@ -2218,13 +2218,13 @@
         <v>23</v>
       </c>
       <c r="G31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
       </c>
       <c r="I31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
@@ -2239,7 +2239,7 @@
         <v>83.08196421090184</v>
       </c>
       <c r="N31">
-        <v>86.23129934518856</v>
+        <v>81.09639830618195</v>
       </c>
       <c r="O31">
         <v>81.32343450062355</v>
@@ -2274,13 +2274,13 @@
         <v>23</v>
       </c>
       <c r="G32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
       </c>
       <c r="I32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
@@ -2295,7 +2295,7 @@
         <v>83.08196421090184</v>
       </c>
       <c r="N32">
-        <v>86.23129934518856</v>
+        <v>81.09639830618195</v>
       </c>
       <c r="O32">
         <v>81.32343450062355</v>
@@ -2307,7 +2307,7 @@
         <v>26</v>
       </c>
       <c r="S32">
-        <v>-5.079931848506192E-05</v>
+        <v>-5.134951838325097</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -2330,13 +2330,13 @@
         <v>23</v>
       </c>
       <c r="G33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
       </c>
       <c r="I33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
@@ -2351,7 +2351,7 @@
         <v>83.08196421090184</v>
       </c>
       <c r="N33">
-        <v>86.23129934518856</v>
+        <v>81.09639830618195</v>
       </c>
       <c r="O33">
         <v>81.32343450062355</v>
@@ -2386,19 +2386,19 @@
         <v>23</v>
       </c>
       <c r="G34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="b">
         <v>0</v>
       </c>
       <c r="I34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
       </c>
       <c r="K34">
-        <v>62.08476673915369</v>
+        <v>62.08476673915371</v>
       </c>
       <c r="L34">
         <v>10.21307356029052</v>
@@ -2407,7 +2407,7 @@
         <v>13.71287131010016</v>
       </c>
       <c r="N34">
-        <v>62.08438679078924</v>
+        <v>13.33471491243047</v>
       </c>
       <c r="O34">
         <v>13.39868311362757</v>
@@ -2419,7 +2419,7 @@
         <v>24</v>
       </c>
       <c r="S34">
-        <v>-51.87169317886318</v>
+        <v>-51.87169317886319</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -2442,19 +2442,19 @@
         <v>23</v>
       </c>
       <c r="G35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
       </c>
       <c r="I35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35">
-        <v>62.08476673915369</v>
+        <v>62.08476673915371</v>
       </c>
       <c r="L35">
         <v>10.21307356029052</v>
@@ -2463,7 +2463,7 @@
         <v>13.71287131010016</v>
       </c>
       <c r="N35">
-        <v>62.08438679078924</v>
+        <v>13.33471491243047</v>
       </c>
       <c r="O35">
         <v>13.39868311362757</v>
@@ -2475,7 +2475,7 @@
         <v>25</v>
       </c>
       <c r="S35">
-        <v>-48.37189542905354</v>
+        <v>-48.37189542905355</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -2498,19 +2498,19 @@
         <v>23</v>
       </c>
       <c r="G36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="b">
         <v>0</v>
       </c>
       <c r="I36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36">
-        <v>62.08476673915369</v>
+        <v>62.08476673915371</v>
       </c>
       <c r="L36">
         <v>10.21307356029052</v>
@@ -2519,7 +2519,7 @@
         <v>13.71287131010016</v>
       </c>
       <c r="N36">
-        <v>62.08438679078924</v>
+        <v>13.33471491243047</v>
       </c>
       <c r="O36">
         <v>13.39868311362757</v>
@@ -2531,7 +2531,7 @@
         <v>26</v>
       </c>
       <c r="S36">
-        <v>-0.0003799483644595369</v>
+        <v>-48.75005182672324</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -2554,19 +2554,19 @@
         <v>23</v>
       </c>
       <c r="G37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="b">
         <v>0</v>
       </c>
       <c r="I37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37">
-        <v>62.08476673915369</v>
+        <v>62.08476673915371</v>
       </c>
       <c r="L37">
         <v>10.21307356029052</v>
@@ -2575,7 +2575,7 @@
         <v>13.71287131010016</v>
       </c>
       <c r="N37">
-        <v>62.08438679078924</v>
+        <v>13.33471491243047</v>
       </c>
       <c r="O37">
         <v>13.39868311362757</v>
@@ -2587,7 +2587,7 @@
         <v>27</v>
       </c>
       <c r="S37">
-        <v>-48.68608362552612</v>
+        <v>-48.68608362552613</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -2631,7 +2631,7 @@
         <v>24.06094976894054</v>
       </c>
       <c r="N38">
-        <v>21.35714655389468</v>
+        <v>21.35715098116492</v>
       </c>
       <c r="O38">
         <v>21.3571509811649</v>
@@ -2687,7 +2687,7 @@
         <v>24.06094976894054</v>
       </c>
       <c r="N39">
-        <v>21.35714655389468</v>
+        <v>21.35715098116492</v>
       </c>
       <c r="O39">
         <v>21.3571509811649</v>
@@ -2743,7 +2743,7 @@
         <v>24.06094976894054</v>
       </c>
       <c r="N40">
-        <v>21.35714655389468</v>
+        <v>21.35715098116492</v>
       </c>
       <c r="O40">
         <v>21.3571509811649</v>
@@ -2755,7 +2755,7 @@
         <v>26</v>
       </c>
       <c r="S40">
-        <v>-4.427270200446642E-06</v>
+        <v>3.885780586188048E-14</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -2799,7 +2799,7 @@
         <v>24.06094976894054</v>
       </c>
       <c r="N41">
-        <v>21.35714655389468</v>
+        <v>21.35715098116492</v>
       </c>
       <c r="O41">
         <v>21.3571509811649</v>
@@ -2855,7 +2855,7 @@
         <v>31.72035374708815</v>
       </c>
       <c r="N42">
-        <v>31.69761585132353</v>
+        <v>31.69759345188883</v>
       </c>
       <c r="O42">
         <v>31.69759345188895</v>
@@ -2911,7 +2911,7 @@
         <v>31.72035374708815</v>
       </c>
       <c r="N43">
-        <v>31.69761585132353</v>
+        <v>31.69759345188883</v>
       </c>
       <c r="O43">
         <v>31.69759345188895</v>
@@ -2967,7 +2967,7 @@
         <v>31.72035374708815</v>
       </c>
       <c r="N44">
-        <v>31.69761585132353</v>
+        <v>31.69759345188883</v>
       </c>
       <c r="O44">
         <v>31.69759345188895</v>
@@ -2979,7 +2979,7 @@
         <v>26</v>
       </c>
       <c r="S44">
-        <v>2.239943467929884E-05</v>
+        <v>-2.220446049250313E-14</v>
       </c>
     </row>
     <row r="45" spans="1:19">
@@ -3023,7 +3023,7 @@
         <v>31.72035374708815</v>
       </c>
       <c r="N45">
-        <v>31.69761585132353</v>
+        <v>31.69759345188883</v>
       </c>
       <c r="O45">
         <v>31.69759345188895</v>
@@ -3079,7 +3079,7 @@
         <v>54.07977053474175</v>
       </c>
       <c r="N46">
-        <v>63.69588706061776</v>
+        <v>63.69587112910109</v>
       </c>
       <c r="O46">
         <v>63.69587112910013</v>
@@ -3135,7 +3135,7 @@
         <v>54.07977053474175</v>
       </c>
       <c r="N47">
-        <v>63.69588706061776</v>
+        <v>63.69587112910109</v>
       </c>
       <c r="O47">
         <v>63.69587112910013</v>
@@ -3191,7 +3191,7 @@
         <v>54.07977053474175</v>
       </c>
       <c r="N48">
-        <v>63.69588706061776</v>
+        <v>63.69587112910109</v>
       </c>
       <c r="O48">
         <v>63.69587112910013</v>
@@ -3203,7 +3203,7 @@
         <v>26</v>
       </c>
       <c r="S48">
-        <v>1.593151659484704E-05</v>
+        <v>-7.771561172376096E-14</v>
       </c>
     </row>
     <row r="49" spans="1:19">
@@ -3247,7 +3247,7 @@
         <v>54.07977053474175</v>
       </c>
       <c r="N49">
-        <v>63.69588706061776</v>
+        <v>63.69587112910109</v>
       </c>
       <c r="O49">
         <v>63.69587112910013</v>
@@ -3303,7 +3303,7 @@
         <v>23.52747467805014</v>
       </c>
       <c r="N50">
-        <v>24.76617340061389</v>
+        <v>24.76618218000425</v>
       </c>
       <c r="O50">
         <v>24.76618218000402</v>
@@ -3359,7 +3359,7 @@
         <v>23.52747467805014</v>
       </c>
       <c r="N51">
-        <v>24.76617340061389</v>
+        <v>24.76618218000425</v>
       </c>
       <c r="O51">
         <v>24.76618218000402</v>
@@ -3415,7 +3415,7 @@
         <v>23.52747467805014</v>
       </c>
       <c r="N52">
-        <v>24.76617340061389</v>
+        <v>24.76618218000425</v>
       </c>
       <c r="O52">
         <v>24.76618218000402</v>
@@ -3427,7 +3427,7 @@
         <v>26</v>
       </c>
       <c r="S52">
-        <v>-8.779390378577112E-06</v>
+        <v>-1.387778780781446E-14</v>
       </c>
     </row>
     <row r="53" spans="1:19">
@@ -3471,7 +3471,7 @@
         <v>23.52747467805014</v>
       </c>
       <c r="N53">
-        <v>24.76617340061389</v>
+        <v>24.76618218000425</v>
       </c>
       <c r="O53">
         <v>24.76618218000402</v>
@@ -3527,7 +3527,7 @@
         <v>54.50671624865102</v>
       </c>
       <c r="N54">
-        <v>59.13503660841513</v>
+        <v>59.13503660841497</v>
       </c>
       <c r="O54">
         <v>55.95985155514701</v>
@@ -3583,7 +3583,7 @@
         <v>54.50671624865102</v>
       </c>
       <c r="N55">
-        <v>59.13503660841513</v>
+        <v>59.13503660841497</v>
       </c>
       <c r="O55">
         <v>55.95985155514701</v>
@@ -3639,7 +3639,7 @@
         <v>54.50671624865102</v>
       </c>
       <c r="N56">
-        <v>59.13503660841513</v>
+        <v>59.13503660841497</v>
       </c>
       <c r="O56">
         <v>55.95985155514701</v>
@@ -3651,7 +3651,7 @@
         <v>26</v>
       </c>
       <c r="S56">
-        <v>8.881784197001252E-14</v>
+        <v>-6.661338147750939E-14</v>
       </c>
     </row>
     <row r="57" spans="1:19">
@@ -3695,7 +3695,7 @@
         <v>54.50671624865102</v>
       </c>
       <c r="N57">
-        <v>59.13503660841513</v>
+        <v>59.13503660841497</v>
       </c>
       <c r="O57">
         <v>55.95985155514701</v>
@@ -3730,7 +3730,7 @@
         <v>45</v>
       </c>
       <c r="G58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" t="b">
         <v>0</v>
@@ -3751,7 +3751,7 @@
         <v>51.90628682586594</v>
       </c>
       <c r="N58">
-        <v>52.11350483720619</v>
+        <v>53.53034565535061</v>
       </c>
       <c r="O58">
         <v>50.65195900542998</v>
@@ -3786,7 +3786,7 @@
         <v>45</v>
       </c>
       <c r="G59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" t="b">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>51.90628682586594</v>
       </c>
       <c r="N59">
-        <v>52.11350483720619</v>
+        <v>53.53034565535061</v>
       </c>
       <c r="O59">
         <v>50.65195900542998</v>
@@ -3842,7 +3842,7 @@
         <v>45</v>
       </c>
       <c r="G60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" t="b">
         <v>0</v>
@@ -3863,7 +3863,7 @@
         <v>51.90628682586594</v>
       </c>
       <c r="N60">
-        <v>52.11350483720619</v>
+        <v>53.53034565535061</v>
       </c>
       <c r="O60">
         <v>50.65195900542998</v>
@@ -3875,7 +3875,7 @@
         <v>26</v>
       </c>
       <c r="S60">
-        <v>-5.893726839900637E-07</v>
+        <v>1.416840228771732</v>
       </c>
     </row>
     <row r="61" spans="1:19">
@@ -3898,7 +3898,7 @@
         <v>45</v>
       </c>
       <c r="G61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="b">
         <v>0</v>
@@ -3919,7 +3919,7 @@
         <v>51.90628682586594</v>
       </c>
       <c r="N61">
-        <v>52.11350483720619</v>
+        <v>53.53034565535061</v>
       </c>
       <c r="O61">
         <v>50.65195900542998</v>
@@ -3975,7 +3975,7 @@
         <v>86.18639189909273</v>
       </c>
       <c r="N62">
-        <v>86.50493846489205</v>
+        <v>86.28323930670892</v>
       </c>
       <c r="O62">
         <v>86.15575534253763</v>
@@ -4031,7 +4031,7 @@
         <v>86.18639189909273</v>
       </c>
       <c r="N63">
-        <v>86.50493846489205</v>
+        <v>86.28323930670892</v>
       </c>
       <c r="O63">
         <v>86.15575534253763</v>
@@ -4087,7 +4087,7 @@
         <v>86.18639189909273</v>
       </c>
       <c r="N64">
-        <v>86.50493846489205</v>
+        <v>86.28323930670892</v>
       </c>
       <c r="O64">
         <v>86.15575534253763</v>
@@ -4099,7 +4099,7 @@
         <v>26</v>
       </c>
       <c r="S64">
-        <v>-0.3675334676580211</v>
+        <v>-0.5892326258411407</v>
       </c>
     </row>
     <row r="65" spans="1:19">
@@ -4143,7 +4143,7 @@
         <v>86.18639189909273</v>
       </c>
       <c r="N65">
-        <v>86.50493846489205</v>
+        <v>86.28323930670892</v>
       </c>
       <c r="O65">
         <v>86.15575534253763</v>
@@ -4199,7 +4199,7 @@
         <v>86.20836635098563</v>
       </c>
       <c r="N66">
-        <v>89.60497394358082</v>
+        <v>89.6049735994483</v>
       </c>
       <c r="O66">
         <v>84.12084906229185</v>
@@ -4255,7 +4255,7 @@
         <v>86.20836635098563</v>
       </c>
       <c r="N67">
-        <v>89.60497394358082</v>
+        <v>89.6049735994483</v>
       </c>
       <c r="O67">
         <v>84.12084906229185</v>
@@ -4311,7 +4311,7 @@
         <v>86.20836635098563</v>
       </c>
       <c r="N68">
-        <v>89.60497394358082</v>
+        <v>89.6049735994483</v>
       </c>
       <c r="O68">
         <v>84.12084906229185</v>
@@ -4323,7 +4323,7 @@
         <v>26</v>
       </c>
       <c r="S68">
-        <v>3.441324780695254E-07</v>
+        <v>-3.33066907387547E-14</v>
       </c>
     </row>
     <row r="69" spans="1:19">
@@ -4367,7 +4367,7 @@
         <v>86.20836635098563</v>
       </c>
       <c r="N69">
-        <v>89.60497394358082</v>
+        <v>89.6049735994483</v>
       </c>
       <c r="O69">
         <v>84.12084906229185</v>
@@ -4402,13 +4402,13 @@
         <v>46</v>
       </c>
       <c r="G70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" t="b">
         <v>0</v>
       </c>
       <c r="I70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" t="b">
         <v>1</v>
@@ -4423,7 +4423,7 @@
         <v>80.80868017899735</v>
       </c>
       <c r="N70">
-        <v>83.57810910606807</v>
+        <v>80.29786188087405</v>
       </c>
       <c r="O70">
         <v>80.2465075257291</v>
@@ -4458,13 +4458,13 @@
         <v>46</v>
       </c>
       <c r="G71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" t="b">
         <v>0</v>
       </c>
       <c r="I71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="b">
         <v>1</v>
@@ -4479,7 +4479,7 @@
         <v>80.80868017899735</v>
       </c>
       <c r="N71">
-        <v>83.57810910606807</v>
+        <v>80.29786188087405</v>
       </c>
       <c r="O71">
         <v>80.2465075257291</v>
@@ -4514,13 +4514,13 @@
         <v>46</v>
       </c>
       <c r="G72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" t="b">
         <v>0</v>
       </c>
       <c r="I72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
@@ -4535,7 +4535,7 @@
         <v>80.80868017899735</v>
       </c>
       <c r="N72">
-        <v>83.57810910606807</v>
+        <v>80.29786188087405</v>
       </c>
       <c r="O72">
         <v>80.2465075257291</v>
@@ -4547,7 +4547,7 @@
         <v>26</v>
       </c>
       <c r="S72">
-        <v>4.998476554884945E-06</v>
+        <v>-3.280242226717456</v>
       </c>
     </row>
     <row r="73" spans="1:19">
@@ -4570,13 +4570,13 @@
         <v>46</v>
       </c>
       <c r="G73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="b">
         <v>0</v>
       </c>
       <c r="I73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="b">
         <v>1</v>
@@ -4591,7 +4591,7 @@
         <v>80.80868017899735</v>
       </c>
       <c r="N73">
-        <v>83.57810910606807</v>
+        <v>80.29786188087405</v>
       </c>
       <c r="O73">
         <v>80.2465075257291</v>
@@ -4626,7 +4626,7 @@
         <v>45</v>
       </c>
       <c r="G74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" t="b">
         <v>0</v>
@@ -4638,7 +4638,7 @@
         <v>0</v>
       </c>
       <c r="K74">
-        <v>57.39094993352768</v>
+        <v>57.3909499335277</v>
       </c>
       <c r="L74">
         <v>89.80584340279077</v>
@@ -4647,7 +4647,7 @@
         <v>85.01223685119706</v>
       </c>
       <c r="N74">
-        <v>57.39093413423676</v>
+        <v>88.65874474703118</v>
       </c>
       <c r="O74">
         <v>88.60850787159013</v>
@@ -4659,7 +4659,7 @@
         <v>24</v>
       </c>
       <c r="S74">
-        <v>32.41489346926308</v>
+        <v>32.41489346926306</v>
       </c>
     </row>
     <row r="75" spans="1:19">
@@ -4682,7 +4682,7 @@
         <v>45</v>
       </c>
       <c r="G75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" t="b">
         <v>0</v>
@@ -4694,7 +4694,7 @@
         <v>0</v>
       </c>
       <c r="K75">
-        <v>57.39094993352768</v>
+        <v>57.3909499335277</v>
       </c>
       <c r="L75">
         <v>89.80584340279077</v>
@@ -4703,7 +4703,7 @@
         <v>85.01223685119706</v>
       </c>
       <c r="N75">
-        <v>57.39093413423676</v>
+        <v>88.65874474703118</v>
       </c>
       <c r="O75">
         <v>88.60850787159013</v>
@@ -4715,7 +4715,7 @@
         <v>25</v>
       </c>
       <c r="S75">
-        <v>27.62128691766937</v>
+        <v>27.62128691766935</v>
       </c>
     </row>
     <row r="76" spans="1:19">
@@ -4738,7 +4738,7 @@
         <v>45</v>
       </c>
       <c r="G76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" t="b">
         <v>0</v>
@@ -4750,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="K76">
-        <v>57.39094993352768</v>
+        <v>57.3909499335277</v>
       </c>
       <c r="L76">
         <v>89.80584340279077</v>
@@ -4759,7 +4759,7 @@
         <v>85.01223685119706</v>
       </c>
       <c r="N76">
-        <v>57.39093413423676</v>
+        <v>88.65874474703118</v>
       </c>
       <c r="O76">
         <v>88.60850787159013</v>
@@ -4771,7 +4771,7 @@
         <v>26</v>
       </c>
       <c r="S76">
-        <v>-1.579929091999333E-05</v>
+        <v>31.26779481350348</v>
       </c>
     </row>
     <row r="77" spans="1:19">
@@ -4794,7 +4794,7 @@
         <v>45</v>
       </c>
       <c r="G77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" t="b">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>0</v>
       </c>
       <c r="K77">
-        <v>57.39094993352768</v>
+        <v>57.3909499335277</v>
       </c>
       <c r="L77">
         <v>89.80584340279077</v>
@@ -4815,7 +4815,7 @@
         <v>85.01223685119706</v>
       </c>
       <c r="N77">
-        <v>57.39093413423676</v>
+        <v>88.65874474703118</v>
       </c>
       <c r="O77">
         <v>88.60850787159013</v>
@@ -4827,7 +4827,7 @@
         <v>27</v>
       </c>
       <c r="S77">
-        <v>31.21755793806246</v>
+        <v>31.21755793806243</v>
       </c>
     </row>
     <row r="78" spans="1:19">
@@ -4871,7 +4871,7 @@
         <v>19.32569731221687</v>
       </c>
       <c r="N78">
-        <v>21.69845309646588</v>
+        <v>21.69862789322196</v>
       </c>
       <c r="O78">
         <v>21.69862789322168</v>
@@ -4927,7 +4927,7 @@
         <v>19.32569731221687</v>
       </c>
       <c r="N79">
-        <v>21.69845309646588</v>
+        <v>21.69862789322196</v>
       </c>
       <c r="O79">
         <v>21.69862789322168</v>
@@ -4983,7 +4983,7 @@
         <v>19.32569731221687</v>
       </c>
       <c r="N80">
-        <v>21.69845309646588</v>
+        <v>21.69862789322196</v>
       </c>
       <c r="O80">
         <v>21.69862789322168</v>
@@ -4995,7 +4995,7 @@
         <v>26</v>
       </c>
       <c r="S80">
-        <v>0.1278648328520093</v>
+        <v>0.1280396296080955</v>
       </c>
     </row>
     <row r="81" spans="1:19">
@@ -5039,7 +5039,7 @@
         <v>19.32569731221687</v>
       </c>
       <c r="N81">
-        <v>21.69845309646588</v>
+        <v>21.69862789322196</v>
       </c>
       <c r="O81">
         <v>21.69862789322168</v>
@@ -5095,7 +5095,7 @@
         <v>34.67954705337402</v>
       </c>
       <c r="N82">
-        <v>32.1691111464876</v>
+        <v>32.16938106949732</v>
       </c>
       <c r="O82">
         <v>32.16938106949767</v>
@@ -5151,7 +5151,7 @@
         <v>34.67954705337402</v>
       </c>
       <c r="N83">
-        <v>32.1691111464876</v>
+        <v>32.16938106949732</v>
       </c>
       <c r="O83">
         <v>32.16938106949767</v>
@@ -5207,7 +5207,7 @@
         <v>34.67954705337402</v>
       </c>
       <c r="N84">
-        <v>32.1691111464876</v>
+        <v>32.16938106949732</v>
       </c>
       <c r="O84">
         <v>32.16938106949767</v>
@@ -5219,7 +5219,7 @@
         <v>26</v>
       </c>
       <c r="S84">
-        <v>0.643564166800864</v>
+        <v>0.6438340898105854</v>
       </c>
     </row>
     <row r="85" spans="1:19">
@@ -5263,7 +5263,7 @@
         <v>34.67954705337402</v>
       </c>
       <c r="N85">
-        <v>32.1691111464876</v>
+        <v>32.16938106949732</v>
       </c>
       <c r="O85">
         <v>32.16938106949767</v>
@@ -5319,7 +5319,7 @@
         <v>49.72767225702409</v>
       </c>
       <c r="N86">
-        <v>60.68935426323825</v>
+        <v>60.68919744821554</v>
       </c>
       <c r="O86">
         <v>60.689197448217</v>
@@ -5375,7 +5375,7 @@
         <v>49.72767225702409</v>
       </c>
       <c r="N87">
-        <v>60.68935426323825</v>
+        <v>60.68919744821554</v>
       </c>
       <c r="O87">
         <v>60.689197448217</v>
@@ -5431,7 +5431,7 @@
         <v>49.72767225702409</v>
       </c>
       <c r="N88">
-        <v>60.68935426323825</v>
+        <v>60.68919744821554</v>
       </c>
       <c r="O88">
         <v>60.689197448217</v>
@@ -5443,7 +5443,7 @@
         <v>26</v>
       </c>
       <c r="S88">
-        <v>0.6497317859935015</v>
+        <v>0.6495749709707899</v>
       </c>
     </row>
     <row r="89" spans="1:19">
@@ -5487,7 +5487,7 @@
         <v>49.72767225702409</v>
       </c>
       <c r="N89">
-        <v>60.68935426323825</v>
+        <v>60.68919744821554</v>
       </c>
       <c r="O89">
         <v>60.689197448217</v>
@@ -5543,7 +5543,7 @@
         <v>22.99034795670897</v>
       </c>
       <c r="N90">
-        <v>23.20126334569809</v>
+        <v>23.20257112329879</v>
       </c>
       <c r="O90">
         <v>23.20256381426609</v>
@@ -5599,7 +5599,7 @@
         <v>22.99034795670897</v>
       </c>
       <c r="N91">
-        <v>23.20126334569809</v>
+        <v>23.20257112329879</v>
       </c>
       <c r="O91">
         <v>23.20256381426609</v>
@@ -5655,7 +5655,7 @@
         <v>22.99034795670897</v>
       </c>
       <c r="N92">
-        <v>23.20126334569809</v>
+        <v>23.20257112329879</v>
       </c>
       <c r="O92">
         <v>23.20256381426609</v>
@@ -5667,7 +5667,7 @@
         <v>26</v>
       </c>
       <c r="S92">
-        <v>0.1940531766436659</v>
+        <v>0.1953609542443641</v>
       </c>
     </row>
     <row r="93" spans="1:19">
@@ -5711,7 +5711,7 @@
         <v>22.99034795670897</v>
       </c>
       <c r="N93">
-        <v>23.20126334569809</v>
+        <v>23.20257112329879</v>
       </c>
       <c r="O93">
         <v>23.20256381426609</v>
@@ -5767,7 +5767,7 @@
         <v>97.37519569804425</v>
       </c>
       <c r="N94">
-        <v>90.0727996222914</v>
+        <v>90.07259667664735</v>
       </c>
       <c r="O94">
         <v>95.57910733008741</v>
@@ -5823,7 +5823,7 @@
         <v>97.37519569804425</v>
       </c>
       <c r="N95">
-        <v>90.0727996222914</v>
+        <v>90.07259667664735</v>
       </c>
       <c r="O95">
         <v>95.57910733008741</v>
@@ -5879,7 +5879,7 @@
         <v>97.37519569804425</v>
       </c>
       <c r="N96">
-        <v>90.0727996222914</v>
+        <v>90.07259667664735</v>
       </c>
       <c r="O96">
         <v>95.57910733008741</v>
@@ -5891,7 +5891,7 @@
         <v>26</v>
       </c>
       <c r="S96">
-        <v>-0.07374473219401434</v>
+        <v>-0.07394767783805989</v>
       </c>
     </row>
     <row r="97" spans="1:19">
@@ -5935,7 +5935,7 @@
         <v>97.37519569804425</v>
       </c>
       <c r="N97">
-        <v>90.0727996222914</v>
+        <v>90.07259667664735</v>
       </c>
       <c r="O97">
         <v>95.57910733008741</v>
@@ -5991,7 +5991,7 @@
         <v>61.83810661418286</v>
       </c>
       <c r="N98">
-        <v>60.38548476569188</v>
+        <v>60.38562654741987</v>
       </c>
       <c r="O98">
         <v>61.5741597734096</v>
@@ -6047,7 +6047,7 @@
         <v>61.83810661418286</v>
       </c>
       <c r="N99">
-        <v>60.38548476569188</v>
+        <v>60.38562654741987</v>
       </c>
       <c r="O99">
         <v>61.5741597734096</v>
@@ -6103,7 +6103,7 @@
         <v>61.83810661418286</v>
       </c>
       <c r="N100">
-        <v>60.38548476569188</v>
+        <v>60.38562654741987</v>
       </c>
       <c r="O100">
         <v>61.5741597734096</v>
@@ -6115,7 +6115,7 @@
         <v>26</v>
       </c>
       <c r="S100">
-        <v>-0.07785244758744536</v>
+        <v>-0.07771066585946507</v>
       </c>
     </row>
     <row r="101" spans="1:19">
@@ -6159,7 +6159,7 @@
         <v>61.83810661418286</v>
       </c>
       <c r="N101">
-        <v>60.38548476569188</v>
+        <v>60.38562654741987</v>
       </c>
       <c r="O101">
         <v>61.5741597734096</v>
@@ -6215,7 +6215,7 @@
         <v>52.0223729574794</v>
       </c>
       <c r="N102">
-        <v>51.95936243888178</v>
+        <v>51.95928079861044</v>
       </c>
       <c r="O102">
         <v>55.30293669507238</v>
@@ -6271,7 +6271,7 @@
         <v>52.0223729574794</v>
       </c>
       <c r="N103">
-        <v>51.95936243888178</v>
+        <v>51.95928079861044</v>
       </c>
       <c r="O103">
         <v>55.30293669507238</v>
@@ -6327,7 +6327,7 @@
         <v>52.0223729574794</v>
       </c>
       <c r="N104">
-        <v>51.95936243888178</v>
+        <v>51.95928079861044</v>
       </c>
       <c r="O104">
         <v>55.30293669507238</v>
@@ -6339,7 +6339,7 @@
         <v>26</v>
       </c>
       <c r="S104">
-        <v>-0.08221133026802274</v>
+        <v>-0.08229297053935491</v>
       </c>
     </row>
     <row r="105" spans="1:19">
@@ -6383,7 +6383,7 @@
         <v>52.0223729574794</v>
       </c>
       <c r="N105">
-        <v>51.95936243888178</v>
+        <v>51.95928079861044</v>
       </c>
       <c r="O105">
         <v>55.30293669507238</v>
@@ -6439,7 +6439,7 @@
         <v>92.8918480815879</v>
       </c>
       <c r="N106">
-        <v>87.32208583041826</v>
+        <v>87.32198154714231</v>
       </c>
       <c r="O106">
         <v>92.33060453033349</v>
@@ -6495,7 +6495,7 @@
         <v>92.8918480815879</v>
       </c>
       <c r="N107">
-        <v>87.32208583041826</v>
+        <v>87.32198154714231</v>
       </c>
       <c r="O107">
         <v>92.33060453033349</v>
@@ -6551,7 +6551,7 @@
         <v>92.8918480815879</v>
       </c>
       <c r="N108">
-        <v>87.32208583041826</v>
+        <v>87.32198154714231</v>
       </c>
       <c r="O108">
         <v>92.33060453033349</v>
@@ -6563,7 +6563,7 @@
         <v>26</v>
       </c>
       <c r="S108">
-        <v>-0.1419314341352229</v>
+        <v>-0.1420357174111708</v>
       </c>
     </row>
     <row r="109" spans="1:19">
@@ -6607,7 +6607,7 @@
         <v>92.8918480815879</v>
       </c>
       <c r="N109">
-        <v>87.32208583041826</v>
+        <v>87.32198154714231</v>
       </c>
       <c r="O109">
         <v>92.33060453033349</v>
@@ -6663,7 +6663,7 @@
         <v>86.08690872264387</v>
       </c>
       <c r="N110">
-        <v>90.3052128531078</v>
+        <v>90.30529632334452</v>
       </c>
       <c r="O110">
         <v>85.10314632445215</v>
@@ -6719,7 +6719,7 @@
         <v>86.08690872264387</v>
       </c>
       <c r="N111">
-        <v>90.3052128531078</v>
+        <v>90.30529632334452</v>
       </c>
       <c r="O111">
         <v>85.10314632445215</v>
@@ -6775,7 +6775,7 @@
         <v>86.08690872264387</v>
       </c>
       <c r="N112">
-        <v>90.3052128531078</v>
+        <v>90.30529632334452</v>
       </c>
       <c r="O112">
         <v>85.10314632445215</v>
@@ -6787,7 +6787,7 @@
         <v>26</v>
       </c>
       <c r="S112">
-        <v>0.07260790867795741</v>
+        <v>0.07269137891467992</v>
       </c>
     </row>
     <row r="113" spans="1:19">
@@ -6831,7 +6831,7 @@
         <v>86.08690872264387</v>
       </c>
       <c r="N113">
-        <v>90.3052128531078</v>
+        <v>90.30529632334452</v>
       </c>
       <c r="O113">
         <v>85.10314632445215</v>
@@ -6866,13 +6866,13 @@
         <v>46</v>
       </c>
       <c r="G114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H114" t="b">
         <v>0</v>
       </c>
       <c r="I114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J114" t="b">
         <v>1</v>
@@ -6887,7 +6887,7 @@
         <v>78.38920705055602</v>
       </c>
       <c r="N114">
-        <v>81.98892103562903</v>
+        <v>78.48140317201236</v>
       </c>
       <c r="O114">
         <v>78.8650035822381</v>
@@ -6922,13 +6922,13 @@
         <v>46</v>
       </c>
       <c r="G115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115" t="b">
         <v>0</v>
       </c>
       <c r="I115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" t="b">
         <v>1</v>
@@ -6943,7 +6943,7 @@
         <v>78.38920705055602</v>
       </c>
       <c r="N115">
-        <v>81.98892103562903</v>
+        <v>78.48140317201236</v>
       </c>
       <c r="O115">
         <v>78.8650035822381</v>
@@ -6978,13 +6978,13 @@
         <v>46</v>
       </c>
       <c r="G116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H116" t="b">
         <v>0</v>
       </c>
       <c r="I116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116" t="b">
         <v>1</v>
@@ -6999,7 +6999,7 @@
         <v>78.38920705055602</v>
       </c>
       <c r="N116">
-        <v>81.98892103562903</v>
+        <v>78.48140317201236</v>
       </c>
       <c r="O116">
         <v>78.8650035822381</v>
@@ -7011,7 +7011,7 @@
         <v>26</v>
       </c>
       <c r="S116">
-        <v>0.1394981718726984</v>
+        <v>-3.368019691743973</v>
       </c>
     </row>
     <row r="117" spans="1:19">
@@ -7034,13 +7034,13 @@
         <v>46</v>
       </c>
       <c r="G117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H117" t="b">
         <v>0</v>
       </c>
       <c r="I117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J117" t="b">
         <v>1</v>
@@ -7055,7 +7055,7 @@
         <v>78.38920705055602</v>
       </c>
       <c r="N117">
-        <v>81.98892103562903</v>
+        <v>78.48140317201236</v>
       </c>
       <c r="O117">
         <v>78.8650035822381</v>
@@ -7090,7 +7090,7 @@
         <v>45</v>
       </c>
       <c r="G118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" t="b">
         <v>0</v>
@@ -7102,7 +7102,7 @@
         <v>0</v>
       </c>
       <c r="K118">
-        <v>61.48854117351643</v>
+        <v>61.48758237299869</v>
       </c>
       <c r="L118">
         <v>15.85204755614267</v>
@@ -7111,7 +7111,7 @@
         <v>27.63313329113416</v>
       </c>
       <c r="N118">
-        <v>61.86903818469865</v>
+        <v>25.61757068892306</v>
       </c>
       <c r="O118">
         <v>26.37036914267005</v>
@@ -7123,7 +7123,7 @@
         <v>24</v>
       </c>
       <c r="S118">
-        <v>-45.63649361737377</v>
+        <v>-45.63553481685603</v>
       </c>
     </row>
     <row r="119" spans="1:19">
@@ -7146,7 +7146,7 @@
         <v>45</v>
       </c>
       <c r="G119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H119" t="b">
         <v>0</v>
@@ -7158,7 +7158,7 @@
         <v>0</v>
       </c>
       <c r="K119">
-        <v>61.48854117351643</v>
+        <v>61.48758237299869</v>
       </c>
       <c r="L119">
         <v>15.85204755614267</v>
@@ -7167,7 +7167,7 @@
         <v>27.63313329113416</v>
       </c>
       <c r="N119">
-        <v>61.86903818469865</v>
+        <v>25.61757068892306</v>
       </c>
       <c r="O119">
         <v>26.37036914267005</v>
@@ -7179,7 +7179,7 @@
         <v>25</v>
       </c>
       <c r="S119">
-        <v>-33.85540788238227</v>
+        <v>-33.85444908186454</v>
       </c>
     </row>
     <row r="120" spans="1:19">
@@ -7202,7 +7202,7 @@
         <v>45</v>
       </c>
       <c r="G120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" t="b">
         <v>0</v>
@@ -7214,7 +7214,7 @@
         <v>0</v>
       </c>
       <c r="K120">
-        <v>61.48854117351643</v>
+        <v>61.48758237299869</v>
       </c>
       <c r="L120">
         <v>15.85204755614267</v>
@@ -7223,7 +7223,7 @@
         <v>27.63313329113416</v>
       </c>
       <c r="N120">
-        <v>61.86903818469865</v>
+        <v>25.61757068892306</v>
       </c>
       <c r="O120">
         <v>26.37036914267005</v>
@@ -7235,7 +7235,7 @@
         <v>26</v>
       </c>
       <c r="S120">
-        <v>0.3804970111822126</v>
+        <v>-35.87001168407564</v>
       </c>
     </row>
     <row r="121" spans="1:19">
@@ -7258,7 +7258,7 @@
         <v>45</v>
       </c>
       <c r="G121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H121" t="b">
         <v>0</v>
@@ -7270,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="K121">
-        <v>61.48854117351643</v>
+        <v>61.48758237299869</v>
       </c>
       <c r="L121">
         <v>15.85204755614267</v>
@@ -7279,7 +7279,7 @@
         <v>27.63313329113416</v>
       </c>
       <c r="N121">
-        <v>61.86903818469865</v>
+        <v>25.61757068892306</v>
       </c>
       <c r="O121">
         <v>26.37036914267005</v>
@@ -7291,7 +7291,7 @@
         <v>27</v>
       </c>
       <c r="S121">
-        <v>-35.11817203084638</v>
+        <v>-35.11721323032864</v>
       </c>
     </row>
     <row r="122" spans="1:19">
@@ -7335,7 +7335,7 @@
         <v>21.0821323119713</v>
       </c>
       <c r="N122">
-        <v>21.31738515744854</v>
+        <v>21.31743546418101</v>
       </c>
       <c r="O122">
         <v>21.31743571607228</v>
@@ -7391,7 +7391,7 @@
         <v>21.0821323119713</v>
       </c>
       <c r="N123">
-        <v>21.31738515744854</v>
+        <v>21.31743546418101</v>
       </c>
       <c r="O123">
         <v>21.31743571607228</v>
@@ -7447,7 +7447,7 @@
         <v>21.0821323119713</v>
       </c>
       <c r="N124">
-        <v>21.31738515744854</v>
+        <v>21.31743546418101</v>
       </c>
       <c r="O124">
         <v>21.31743571607228</v>
@@ -7459,7 +7459,7 @@
         <v>26</v>
       </c>
       <c r="S124">
-        <v>-5.055862353497975E-05</v>
+        <v>-2.518910607873792E-07</v>
       </c>
     </row>
     <row r="125" spans="1:19">
@@ -7503,7 +7503,7 @@
         <v>21.0821323119713</v>
       </c>
       <c r="N125">
-        <v>21.31738515744854</v>
+        <v>21.31743546418101</v>
       </c>
       <c r="O125">
         <v>21.31743571607228</v>
@@ -7559,7 +7559,7 @@
         <v>30.75675385629721</v>
       </c>
       <c r="N126">
-        <v>30.53787388404202</v>
+        <v>30.53773391394778</v>
       </c>
       <c r="O126">
         <v>30.53774451303552</v>
@@ -7615,7 +7615,7 @@
         <v>30.75675385629721</v>
       </c>
       <c r="N127">
-        <v>30.53787388404202</v>
+        <v>30.53773391394778</v>
       </c>
       <c r="O127">
         <v>30.53774451303552</v>
@@ -7671,7 +7671,7 @@
         <v>30.75675385629721</v>
       </c>
       <c r="N128">
-        <v>30.53787388404202</v>
+        <v>30.53773391394778</v>
       </c>
       <c r="O128">
         <v>30.53774451303552</v>
@@ -7683,7 +7683,7 @@
         <v>26</v>
       </c>
       <c r="S128">
-        <v>0.0001293710063798859</v>
+        <v>-1.059908785738806E-05</v>
       </c>
     </row>
     <row r="129" spans="1:19">
@@ -7727,7 +7727,7 @@
         <v>30.75675385629721</v>
       </c>
       <c r="N129">
-        <v>30.53787388404202</v>
+        <v>30.53773391394778</v>
       </c>
       <c r="O129">
         <v>30.53774451303552</v>
@@ -7783,7 +7783,7 @@
         <v>45.8582452259475</v>
       </c>
       <c r="N130">
-        <v>60.07047391727885</v>
+        <v>60.07053306006303</v>
       </c>
       <c r="O130">
         <v>60.07051969567506</v>
@@ -7839,7 +7839,7 @@
         <v>45.8582452259475</v>
       </c>
       <c r="N131">
-        <v>60.07047391727885</v>
+        <v>60.07053306006303</v>
       </c>
       <c r="O131">
         <v>60.07051969567506</v>
@@ -7895,7 +7895,7 @@
         <v>45.8582452259475</v>
       </c>
       <c r="N132">
-        <v>60.07047391727885</v>
+        <v>60.07053306006303</v>
       </c>
       <c r="O132">
         <v>60.07051969567506</v>
@@ -7907,7 +7907,7 @@
         <v>26</v>
       </c>
       <c r="S132">
-        <v>-4.577839528563388E-05</v>
+        <v>1.336438889554259E-05</v>
       </c>
     </row>
     <row r="133" spans="1:19">
@@ -7951,7 +7951,7 @@
         <v>45.8582452259475</v>
       </c>
       <c r="N133">
-        <v>60.07047391727885</v>
+        <v>60.07053306006303</v>
       </c>
       <c r="O133">
         <v>60.07051969567506</v>
@@ -8007,7 +8007,7 @@
         <v>22.39021566833954</v>
       </c>
       <c r="N134">
-        <v>22.80754691627862</v>
+        <v>22.80764163600191</v>
       </c>
       <c r="O134">
         <v>22.80764277056693</v>
@@ -8063,7 +8063,7 @@
         <v>22.39021566833954</v>
       </c>
       <c r="N135">
-        <v>22.80754691627862</v>
+        <v>22.80764163600191</v>
       </c>
       <c r="O135">
         <v>22.80764277056693</v>
@@ -8119,7 +8119,7 @@
         <v>22.39021566833954</v>
       </c>
       <c r="N136">
-        <v>22.80754691627862</v>
+        <v>22.80764163600191</v>
       </c>
       <c r="O136">
         <v>22.80764277056693</v>
@@ -8131,7 +8131,7 @@
         <v>26</v>
       </c>
       <c r="S136">
-        <v>-9.585428886738079E-05</v>
+        <v>-1.134565577598501E-06</v>
       </c>
     </row>
     <row r="137" spans="1:19">
@@ -8175,7 +8175,7 @@
         <v>22.39021566833954</v>
       </c>
       <c r="N137">
-        <v>22.80754691627862</v>
+        <v>22.80764163600191</v>
       </c>
       <c r="O137">
         <v>22.80764277056693</v>
@@ -8231,7 +8231,7 @@
         <v>97.72217750828189</v>
       </c>
       <c r="N138">
-        <v>89.05765887555872</v>
+        <v>89.05721624984083</v>
       </c>
       <c r="O138">
         <v>96.55148821708075</v>
@@ -8287,7 +8287,7 @@
         <v>97.72217750828189</v>
       </c>
       <c r="N139">
-        <v>89.05765887555872</v>
+        <v>89.05721624984083</v>
       </c>
       <c r="O139">
         <v>96.55148821708075</v>
@@ -8343,7 +8343,7 @@
         <v>97.72217750828189</v>
       </c>
       <c r="N140">
-        <v>89.05765887555872</v>
+        <v>89.05721624984083</v>
       </c>
       <c r="O140">
         <v>96.55148821708075</v>
@@ -8355,7 +8355,7 @@
         <v>26</v>
       </c>
       <c r="S140">
-        <v>0.0004420887326217482</v>
+        <v>-5.369852673631215E-07</v>
       </c>
     </row>
     <row r="141" spans="1:19">
@@ -8399,7 +8399,7 @@
         <v>97.72217750828189</v>
       </c>
       <c r="N141">
-        <v>89.05765887555872</v>
+        <v>89.05721624984083</v>
       </c>
       <c r="O141">
         <v>96.55148821708075</v>
@@ -8455,7 +8455,7 @@
         <v>60.91237054764949</v>
       </c>
       <c r="N142">
-        <v>61.88487446389005</v>
+        <v>61.88492674501148</v>
       </c>
       <c r="O142">
         <v>61.79791610360936</v>
@@ -8511,7 +8511,7 @@
         <v>60.91237054764949</v>
       </c>
       <c r="N143">
-        <v>61.88487446389005</v>
+        <v>61.88492674501148</v>
       </c>
       <c r="O143">
         <v>61.79791610360936</v>
@@ -8567,7 +8567,7 @@
         <v>60.91237054764949</v>
       </c>
       <c r="N144">
-        <v>61.88487446389005</v>
+        <v>61.88492674501148</v>
       </c>
       <c r="O144">
         <v>61.79791610360936</v>
@@ -8579,7 +8579,7 @@
         <v>26</v>
       </c>
       <c r="S144">
-        <v>-5.499686380749935E-05</v>
+        <v>-2.715742375425378E-06</v>
       </c>
     </row>
     <row r="145" spans="1:19">
@@ -8623,7 +8623,7 @@
         <v>60.91237054764949</v>
       </c>
       <c r="N145">
-        <v>61.88487446389005</v>
+        <v>61.88492674501148</v>
       </c>
       <c r="O145">
         <v>61.79791610360936</v>
@@ -8679,7 +8679,7 @@
         <v>51.92607014347461</v>
       </c>
       <c r="N146">
-        <v>52.10415260849751</v>
+        <v>52.10420743694115</v>
       </c>
       <c r="O146">
         <v>53.86689364015055</v>
@@ -8735,7 +8735,7 @@
         <v>51.92607014347461</v>
       </c>
       <c r="N147">
-        <v>52.10415260849751</v>
+        <v>52.10420743694115</v>
       </c>
       <c r="O147">
         <v>53.86689364015055</v>
@@ -8791,7 +8791,7 @@
         <v>51.92607014347461</v>
       </c>
       <c r="N148">
-        <v>52.10415260849751</v>
+        <v>52.10420743694115</v>
       </c>
       <c r="O148">
         <v>53.86689364015055</v>
@@ -8803,7 +8803,7 @@
         <v>26</v>
       </c>
       <c r="S148">
-        <v>-5.48284446955094E-05</v>
+        <v>-1.054711873393899E-12</v>
       </c>
     </row>
     <row r="149" spans="1:19">
@@ -8847,7 +8847,7 @@
         <v>51.92607014347461</v>
       </c>
       <c r="N149">
-        <v>52.10415260849751</v>
+        <v>52.10420743694115</v>
       </c>
       <c r="O149">
         <v>53.86689364015055</v>
@@ -8903,7 +8903,7 @@
         <v>93.81746123745791</v>
       </c>
       <c r="N150">
-        <v>88.10979995491822</v>
+        <v>88.10966088421772</v>
       </c>
       <c r="O150">
         <v>92.81918368316707</v>
@@ -8959,7 +8959,7 @@
         <v>93.81746123745791</v>
       </c>
       <c r="N151">
-        <v>88.10979995491822</v>
+        <v>88.10966088421772</v>
       </c>
       <c r="O151">
         <v>92.81918368316707</v>
@@ -9015,7 +9015,7 @@
         <v>93.81746123745791</v>
       </c>
       <c r="N152">
-        <v>88.10979995491822</v>
+        <v>88.10966088421772</v>
       </c>
       <c r="O152">
         <v>92.81918368316707</v>
@@ -9027,7 +9027,7 @@
         <v>26</v>
       </c>
       <c r="S152">
-        <v>0.0001387844990818898</v>
+        <v>-2.862014181204131E-07</v>
       </c>
     </row>
     <row r="153" spans="1:19">
@@ -9071,7 +9071,7 @@
         <v>93.81746123745791</v>
       </c>
       <c r="N153">
-        <v>88.10979995491822</v>
+        <v>88.10966088421772</v>
       </c>
       <c r="O153">
         <v>92.81918368316707</v>
@@ -9127,7 +9127,7 @@
         <v>87.33730908371679</v>
       </c>
       <c r="N154">
-        <v>90.5964140244042</v>
+        <v>90.59652362315212</v>
       </c>
       <c r="O154">
         <v>86.38402258793528</v>
@@ -9183,7 +9183,7 @@
         <v>87.33730908371679</v>
       </c>
       <c r="N155">
-        <v>90.5964140244042</v>
+        <v>90.59652362315212</v>
       </c>
       <c r="O155">
         <v>86.38402258793528</v>
@@ -9239,7 +9239,7 @@
         <v>87.33730908371679</v>
       </c>
       <c r="N156">
-        <v>90.5964140244042</v>
+        <v>90.59652362315212</v>
       </c>
       <c r="O156">
         <v>86.38402258793528</v>
@@ -9251,7 +9251,7 @@
         <v>26</v>
       </c>
       <c r="S156">
-        <v>-0.0001096041068016085</v>
+        <v>-5.358880006411937E-09</v>
       </c>
     </row>
     <row r="157" spans="1:19">
@@ -9295,7 +9295,7 @@
         <v>87.33730908371679</v>
       </c>
       <c r="N157">
-        <v>90.5964140244042</v>
+        <v>90.59652362315212</v>
       </c>
       <c r="O157">
         <v>86.38402258793528</v>
@@ -9330,13 +9330,13 @@
         <v>46</v>
       </c>
       <c r="G158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H158" t="b">
         <v>0</v>
       </c>
       <c r="I158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J158" t="b">
         <v>1</v>
@@ -9351,7 +9351,7 @@
         <v>77.13851444499748</v>
       </c>
       <c r="N158">
-        <v>81.45051336435527</v>
+        <v>77.06486794272013</v>
       </c>
       <c r="O158">
         <v>77.50558280138344</v>
@@ -9386,13 +9386,13 @@
         <v>46</v>
       </c>
       <c r="G159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H159" t="b">
         <v>0</v>
       </c>
       <c r="I159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J159" t="b">
         <v>1</v>
@@ -9407,7 +9407,7 @@
         <v>77.13851444499748</v>
       </c>
       <c r="N159">
-        <v>81.45051336435527</v>
+        <v>77.06486794272013</v>
       </c>
       <c r="O159">
         <v>77.50558280138344</v>
@@ -9442,13 +9442,13 @@
         <v>46</v>
       </c>
       <c r="G160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H160" t="b">
         <v>0</v>
       </c>
       <c r="I160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J160" t="b">
         <v>1</v>
@@ -9463,7 +9463,7 @@
         <v>77.13851444499748</v>
       </c>
       <c r="N160">
-        <v>81.45051336435527</v>
+        <v>77.06486794272013</v>
       </c>
       <c r="O160">
         <v>77.50558280138344</v>
@@ -9475,7 +9475,7 @@
         <v>26</v>
       </c>
       <c r="S160">
-        <v>1.720158793183657E-05</v>
+        <v>-4.385628220047211</v>
       </c>
     </row>
     <row r="161" spans="1:19">
@@ -9498,13 +9498,13 @@
         <v>46</v>
       </c>
       <c r="G161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H161" t="b">
         <v>0</v>
       </c>
       <c r="I161" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J161" t="b">
         <v>1</v>
@@ -9519,7 +9519,7 @@
         <v>77.13851444499748</v>
       </c>
       <c r="N161">
-        <v>81.45051336435527</v>
+        <v>77.06486794272013</v>
       </c>
       <c r="O161">
         <v>77.50558280138344</v>
@@ -9554,7 +9554,7 @@
         <v>45</v>
       </c>
       <c r="G162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H162" t="b">
         <v>0</v>
@@ -9566,7 +9566,7 @@
         <v>0</v>
       </c>
       <c r="K162">
-        <v>53.97823345914073</v>
+        <v>53.9917012472936</v>
       </c>
       <c r="L162">
         <v>93.32799321490836</v>
@@ -9575,7 +9575,7 @@
         <v>94.92427958065988</v>
       </c>
       <c r="N162">
-        <v>53.97910565701377</v>
+        <v>90.8697488089028</v>
       </c>
       <c r="O162">
         <v>90.81242185197034</v>
@@ -9587,7 +9587,7 @@
         <v>24</v>
       </c>
       <c r="S162">
-        <v>39.34975975576762</v>
+        <v>39.33629196761476</v>
       </c>
     </row>
     <row r="163" spans="1:19">
@@ -9610,7 +9610,7 @@
         <v>45</v>
       </c>
       <c r="G163" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H163" t="b">
         <v>0</v>
@@ -9622,7 +9622,7 @@
         <v>0</v>
       </c>
       <c r="K163">
-        <v>53.97823345914073</v>
+        <v>53.9917012472936</v>
       </c>
       <c r="L163">
         <v>93.32799321490836</v>
@@ -9631,7 +9631,7 @@
         <v>94.92427958065988</v>
       </c>
       <c r="N163">
-        <v>53.97910565701377</v>
+        <v>90.8697488089028</v>
       </c>
       <c r="O163">
         <v>90.81242185197034</v>
@@ -9643,7 +9643,7 @@
         <v>25</v>
       </c>
       <c r="S163">
-        <v>40.94604612151915</v>
+        <v>40.93257833336629</v>
       </c>
     </row>
     <row r="164" spans="1:19">
@@ -9666,7 +9666,7 @@
         <v>45</v>
       </c>
       <c r="G164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H164" t="b">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>0</v>
       </c>
       <c r="K164">
-        <v>53.97823345914073</v>
+        <v>53.9917012472936</v>
       </c>
       <c r="L164">
         <v>93.32799321490836</v>
@@ -9687,7 +9687,7 @@
         <v>94.92427958065988</v>
       </c>
       <c r="N164">
-        <v>53.97910565701377</v>
+        <v>90.8697488089028</v>
       </c>
       <c r="O164">
         <v>90.81242185197034</v>
@@ -9699,7 +9699,7 @@
         <v>26</v>
       </c>
       <c r="S164">
-        <v>0.0008721978730363844</v>
+        <v>36.87804756160919</v>
       </c>
     </row>
     <row r="165" spans="1:19">
@@ -9722,7 +9722,7 @@
         <v>45</v>
       </c>
       <c r="G165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H165" t="b">
         <v>0</v>
@@ -9734,7 +9734,7 @@
         <v>0</v>
       </c>
       <c r="K165">
-        <v>53.97823345914073</v>
+        <v>53.9917012472936</v>
       </c>
       <c r="L165">
         <v>93.32799321490836</v>
@@ -9743,7 +9743,7 @@
         <v>94.92427958065988</v>
       </c>
       <c r="N165">
-        <v>53.97910565701377</v>
+        <v>90.8697488089028</v>
       </c>
       <c r="O165">
         <v>90.81242185197034</v>
@@ -9755,7 +9755,7 @@
         <v>27</v>
       </c>
       <c r="S165">
-        <v>36.8341883928296</v>
+        <v>36.82072060467674</v>
       </c>
     </row>
     <row r="166" spans="1:19">
@@ -9799,7 +9799,7 @@
         <v>21.30356609368213</v>
       </c>
       <c r="N166">
-        <v>21.2269824066753</v>
+        <v>21.22698328526762</v>
       </c>
       <c r="O166">
         <v>21.22698328526727</v>
@@ -9855,7 +9855,7 @@
         <v>21.30356609368213</v>
       </c>
       <c r="N167">
-        <v>21.2269824066753</v>
+        <v>21.22698328526762</v>
       </c>
       <c r="O167">
         <v>21.22698328526727</v>
@@ -9911,7 +9911,7 @@
         <v>21.30356609368213</v>
       </c>
       <c r="N168">
-        <v>21.2269824066753</v>
+        <v>21.22698328526762</v>
       </c>
       <c r="O168">
         <v>21.22698328526727</v>
@@ -9923,7 +9923,7 @@
         <v>26</v>
       </c>
       <c r="S168">
-        <v>-8.785923072407442E-07</v>
+        <v>8.326672684688674E-15</v>
       </c>
     </row>
     <row r="169" spans="1:19">
@@ -9967,7 +9967,7 @@
         <v>21.30356609368213</v>
       </c>
       <c r="N169">
-        <v>21.2269824066753</v>
+        <v>21.22698328526762</v>
       </c>
       <c r="O169">
         <v>21.22698328526727</v>
@@ -10023,7 +10023,7 @@
         <v>31.49768117328373</v>
       </c>
       <c r="N170">
-        <v>30.2156592748536</v>
+        <v>30.21566715129615</v>
       </c>
       <c r="O170">
         <v>30.2156671512971</v>
@@ -10079,7 +10079,7 @@
         <v>31.49768117328373</v>
       </c>
       <c r="N171">
-        <v>30.2156592748536</v>
+        <v>30.21566715129615</v>
       </c>
       <c r="O171">
         <v>30.2156671512971</v>
@@ -10135,7 +10135,7 @@
         <v>31.49768117328373</v>
       </c>
       <c r="N172">
-        <v>30.2156592748536</v>
+        <v>30.21566715129615</v>
       </c>
       <c r="O172">
         <v>30.2156671512971</v>
@@ -10147,7 +10147,7 @@
         <v>26</v>
       </c>
       <c r="S172">
-        <v>-7.876442453813581E-06</v>
+        <v>9.436895709313831E-14</v>
       </c>
     </row>
     <row r="173" spans="1:19">
@@ -10191,7 +10191,7 @@
         <v>31.49768117328373</v>
       </c>
       <c r="N173">
-        <v>30.2156592748536</v>
+        <v>30.21566715129615</v>
       </c>
       <c r="O173">
         <v>30.2156671512971</v>
@@ -10247,7 +10247,7 @@
         <v>48.37082825560479</v>
       </c>
       <c r="N174">
-        <v>60.37578195772038</v>
+        <v>60.37577965233124</v>
       </c>
       <c r="O174">
         <v>60.37577965233331</v>
@@ -10303,7 +10303,7 @@
         <v>48.37082825560479</v>
       </c>
       <c r="N175">
-        <v>60.37578195772038</v>
+        <v>60.37577965233124</v>
       </c>
       <c r="O175">
         <v>60.37577965233331</v>
@@ -10359,7 +10359,7 @@
         <v>48.37082825560479</v>
       </c>
       <c r="N176">
-        <v>60.37578195772038</v>
+        <v>60.37577965233124</v>
       </c>
       <c r="O176">
         <v>60.37577965233331</v>
@@ -10371,7 +10371,7 @@
         <v>26</v>
       </c>
       <c r="S176">
-        <v>2.305388990819779E-06</v>
+        <v>-1.443289932012704E-13</v>
       </c>
     </row>
     <row r="177" spans="1:19">
@@ -10415,7 +10415,7 @@
         <v>48.37082825560479</v>
       </c>
       <c r="N177">
-        <v>60.37578195772038</v>
+        <v>60.37577965233124</v>
       </c>
       <c r="O177">
         <v>60.37577965233331</v>
@@ -10471,7 +10471,7 @@
         <v>23.58081936844238</v>
       </c>
       <c r="N178">
-        <v>22.97492076190164</v>
+        <v>22.97492199572428</v>
       </c>
       <c r="O178">
         <v>22.97492199572342</v>
@@ -10527,7 +10527,7 @@
         <v>23.58081936844238</v>
       </c>
       <c r="N179">
-        <v>22.97492076190164</v>
+        <v>22.97492199572428</v>
       </c>
       <c r="O179">
         <v>22.97492199572342</v>
@@ -10583,7 +10583,7 @@
         <v>23.58081936844238</v>
       </c>
       <c r="N180">
-        <v>22.97492076190164</v>
+        <v>22.97492199572428</v>
       </c>
       <c r="O180">
         <v>22.97492199572342</v>
@@ -10595,7 +10595,7 @@
         <v>26</v>
       </c>
       <c r="S180">
-        <v>-1.233822546908847E-06</v>
+        <v>9.159339953157541E-14</v>
       </c>
     </row>
     <row r="181" spans="1:19">
@@ -10639,7 +10639,7 @@
         <v>23.58081936844238</v>
       </c>
       <c r="N181">
-        <v>22.97492076190164</v>
+        <v>22.97492199572428</v>
       </c>
       <c r="O181">
         <v>22.97492199572342</v>
@@ -10695,7 +10695,7 @@
         <v>96.88576193758112</v>
       </c>
       <c r="N182">
-        <v>88.59255257157727</v>
+        <v>88.59254555058349</v>
       </c>
       <c r="O182">
         <v>96.34417062086995</v>
@@ -10751,7 +10751,7 @@
         <v>96.88576193758112</v>
       </c>
       <c r="N183">
-        <v>88.59255257157727</v>
+        <v>88.59254555058349</v>
       </c>
       <c r="O183">
         <v>96.34417062086995</v>
@@ -10807,7 +10807,7 @@
         <v>96.88576193758112</v>
       </c>
       <c r="N184">
-        <v>88.59255257157727</v>
+        <v>88.59254555058349</v>
       </c>
       <c r="O184">
         <v>96.34417062086995</v>
@@ -10819,7 +10819,7 @@
         <v>26</v>
       </c>
       <c r="S184">
-        <v>7.020993719741853E-06</v>
+        <v>-4.440892098500626E-14</v>
       </c>
     </row>
     <row r="185" spans="1:19">
@@ -10863,7 +10863,7 @@
         <v>96.88576193758112</v>
       </c>
       <c r="N185">
-        <v>88.59255257157727</v>
+        <v>88.59254555058349</v>
       </c>
       <c r="O185">
         <v>96.34417062086995</v>
@@ -10919,7 +10919,7 @@
         <v>62.36779811000003</v>
       </c>
       <c r="N186">
-        <v>60.62870987155611</v>
+        <v>60.62870890285617</v>
       </c>
       <c r="O186">
         <v>61.57279576403442</v>
@@ -10975,7 +10975,7 @@
         <v>62.36779811000003</v>
       </c>
       <c r="N187">
-        <v>60.62870987155611</v>
+        <v>60.62870890285617</v>
       </c>
       <c r="O187">
         <v>61.57279576403442</v>
@@ -11031,7 +11031,7 @@
         <v>62.36779811000003</v>
       </c>
       <c r="N188">
-        <v>60.62870987155611</v>
+        <v>60.62870890285617</v>
       </c>
       <c r="O188">
         <v>61.57279576403442</v>
@@ -11043,7 +11043,7 @@
         <v>26</v>
       </c>
       <c r="S188">
-        <v>9.687000757097053E-07</v>
+        <v>1.332267629550188E-13</v>
       </c>
     </row>
     <row r="189" spans="1:19">
@@ -11087,7 +11087,7 @@
         <v>62.36779811000003</v>
       </c>
       <c r="N189">
-        <v>60.62870987155611</v>
+        <v>60.62870890285617</v>
       </c>
       <c r="O189">
         <v>61.57279576403442</v>
@@ -11143,7 +11143,7 @@
         <v>51.85862400157944</v>
       </c>
       <c r="N190">
-        <v>52.0642385811301</v>
+        <v>52.06423858112995</v>
       </c>
       <c r="O190">
         <v>53.52312405329561</v>
@@ -11199,7 +11199,7 @@
         <v>51.85862400157944</v>
       </c>
       <c r="N191">
-        <v>52.0642385811301</v>
+        <v>52.06423858112995</v>
       </c>
       <c r="O191">
         <v>53.52312405329561</v>
@@ -11255,7 +11255,7 @@
         <v>51.85862400157944</v>
       </c>
       <c r="N192">
-        <v>52.0642385811301</v>
+        <v>52.06423858112995</v>
       </c>
       <c r="O192">
         <v>53.52312405329561</v>
@@ -11267,7 +11267,7 @@
         <v>26</v>
       </c>
       <c r="S192">
-        <v>3.33066907387547E-14</v>
+        <v>-1.110223024625157E-13</v>
       </c>
     </row>
     <row r="193" spans="1:19">
@@ -11311,7 +11311,7 @@
         <v>51.85862400157944</v>
       </c>
       <c r="N193">
-        <v>52.0642385811301</v>
+        <v>52.06423858112995</v>
       </c>
       <c r="O193">
         <v>53.52312405329561</v>
@@ -11367,7 +11367,7 @@
         <v>93.15391473025574</v>
       </c>
       <c r="N194">
-        <v>88.30667213721645</v>
+        <v>88.30666955144453</v>
       </c>
       <c r="O194">
         <v>92.51425156378021</v>
@@ -11423,7 +11423,7 @@
         <v>93.15391473025574</v>
       </c>
       <c r="N195">
-        <v>88.30667213721645</v>
+        <v>88.30666955144453</v>
       </c>
       <c r="O195">
         <v>92.51425156378021</v>
@@ -11479,7 +11479,7 @@
         <v>93.15391473025574</v>
       </c>
       <c r="N196">
-        <v>88.30667213721645</v>
+        <v>88.30666955144453</v>
       </c>
       <c r="O196">
         <v>92.51425156378021</v>
@@ -11491,7 +11491,7 @@
         <v>26</v>
       </c>
       <c r="S196">
-        <v>2.585772018726118E-06</v>
+        <v>8.881784197001252E-14</v>
       </c>
     </row>
     <row r="197" spans="1:19">
@@ -11535,7 +11535,7 @@
         <v>93.15391473025574</v>
       </c>
       <c r="N197">
-        <v>88.30667213721645</v>
+        <v>88.30666955144453</v>
       </c>
       <c r="O197">
         <v>92.51425156378021</v>
@@ -11591,7 +11591,7 @@
         <v>87.77610121354391</v>
       </c>
       <c r="N198">
-        <v>91.13465254586495</v>
+        <v>91.13465758695082</v>
       </c>
       <c r="O198">
         <v>87.3248842206976</v>
@@ -11647,7 +11647,7 @@
         <v>87.77610121354391</v>
       </c>
       <c r="N199">
-        <v>91.13465254586495</v>
+        <v>91.13465758695082</v>
       </c>
       <c r="O199">
         <v>87.3248842206976</v>
@@ -11703,7 +11703,7 @@
         <v>87.77610121354391</v>
       </c>
       <c r="N200">
-        <v>91.13465254586495</v>
+        <v>91.13465758695082</v>
       </c>
       <c r="O200">
         <v>87.3248842206976</v>
@@ -11715,7 +11715,7 @@
         <v>26</v>
       </c>
       <c r="S200">
-        <v>-5.041085948676027E-06</v>
+        <v>-6.661338147750939E-14</v>
       </c>
     </row>
     <row r="201" spans="1:19">
@@ -11759,7 +11759,7 @@
         <v>87.77610121354391</v>
       </c>
       <c r="N201">
-        <v>91.13465254586495</v>
+        <v>91.13465758695082</v>
       </c>
       <c r="O201">
         <v>87.3248842206976</v>
@@ -11794,13 +11794,13 @@
         <v>46</v>
       </c>
       <c r="G202" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H202" t="b">
         <v>0</v>
       </c>
       <c r="I202" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J202" t="b">
         <v>1</v>
@@ -11815,7 +11815,7 @@
         <v>76.90066293725863</v>
       </c>
       <c r="N202">
-        <v>79.06613567717949</v>
+        <v>75.56849142432917</v>
       </c>
       <c r="O202">
         <v>75.97458212096075</v>
@@ -11850,13 +11850,13 @@
         <v>46</v>
       </c>
       <c r="G203" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H203" t="b">
         <v>0</v>
       </c>
       <c r="I203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J203" t="b">
         <v>1</v>
@@ -11871,7 +11871,7 @@
         <v>76.90066293725863</v>
       </c>
       <c r="N203">
-        <v>79.06613567717949</v>
+        <v>75.56849142432917</v>
       </c>
       <c r="O203">
         <v>75.97458212096075</v>
@@ -11906,13 +11906,13 @@
         <v>46</v>
       </c>
       <c r="G204" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H204" t="b">
         <v>0</v>
       </c>
       <c r="I204" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J204" t="b">
         <v>1</v>
@@ -11927,7 +11927,7 @@
         <v>76.90066293725863</v>
       </c>
       <c r="N204">
-        <v>79.06613567717949</v>
+        <v>75.56849142432917</v>
       </c>
       <c r="O204">
         <v>75.97458212096075</v>
@@ -11939,7 +11939,7 @@
         <v>26</v>
       </c>
       <c r="S204">
-        <v>-4.144086362956045E-06</v>
+        <v>-3.497648396936692</v>
       </c>
     </row>
     <row r="205" spans="1:19">
@@ -11962,13 +11962,13 @@
         <v>46</v>
       </c>
       <c r="G205" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H205" t="b">
         <v>0</v>
       </c>
       <c r="I205" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J205" t="b">
         <v>1</v>
@@ -11983,7 +11983,7 @@
         <v>76.90066293725863</v>
       </c>
       <c r="N205">
-        <v>79.06613567717949</v>
+        <v>75.56849142432917</v>
       </c>
       <c r="O205">
         <v>75.97458212096075</v>
@@ -12018,19 +12018,19 @@
         <v>46</v>
       </c>
       <c r="G206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H206" t="b">
         <v>0</v>
       </c>
       <c r="I206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J206" t="b">
         <v>1</v>
       </c>
       <c r="K206">
-        <v>66.17720451206469</v>
+        <v>66.13023562229581</v>
       </c>
       <c r="L206">
         <v>20.45869883040936</v>
@@ -12039,7 +12039,7 @@
         <v>16.07245691629453</v>
       </c>
       <c r="N206">
-        <v>66.17718665643571</v>
+        <v>23.44149865543357</v>
       </c>
       <c r="O206">
         <v>23.28590402691404</v>
@@ -12051,7 +12051,7 @@
         <v>24</v>
       </c>
       <c r="S206">
-        <v>-45.71850568165533</v>
+        <v>-45.67153679188645</v>
       </c>
     </row>
     <row r="207" spans="1:19">
@@ -12074,19 +12074,19 @@
         <v>46</v>
       </c>
       <c r="G207" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H207" t="b">
         <v>0</v>
       </c>
       <c r="I207" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J207" t="b">
         <v>1</v>
       </c>
       <c r="K207">
-        <v>66.17720451206469</v>
+        <v>66.13023562229581</v>
       </c>
       <c r="L207">
         <v>20.45869883040936</v>
@@ -12095,7 +12095,7 @@
         <v>16.07245691629453</v>
       </c>
       <c r="N207">
-        <v>66.17718665643571</v>
+        <v>23.44149865543357</v>
       </c>
       <c r="O207">
         <v>23.28590402691404</v>
@@ -12107,7 +12107,7 @@
         <v>25</v>
       </c>
       <c r="S207">
-        <v>-50.10474759577016</v>
+        <v>-50.05777870600128</v>
       </c>
     </row>
     <row r="208" spans="1:19">
@@ -12130,19 +12130,19 @@
         <v>46</v>
       </c>
       <c r="G208" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H208" t="b">
         <v>0</v>
       </c>
       <c r="I208" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J208" t="b">
         <v>1</v>
       </c>
       <c r="K208">
-        <v>66.17720451206469</v>
+        <v>66.13023562229581</v>
       </c>
       <c r="L208">
         <v>20.45869883040936</v>
@@ -12151,7 +12151,7 @@
         <v>16.07245691629453</v>
       </c>
       <c r="N208">
-        <v>66.17718665643571</v>
+        <v>23.44149865543357</v>
       </c>
       <c r="O208">
         <v>23.28590402691404</v>
@@ -12163,7 +12163,7 @@
         <v>26</v>
       </c>
       <c r="S208">
-        <v>-1.785562898648507E-05</v>
+        <v>-42.68873696686224</v>
       </c>
     </row>
     <row r="209" spans="1:19">
@@ -12186,19 +12186,19 @@
         <v>46</v>
       </c>
       <c r="G209" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H209" t="b">
         <v>0</v>
       </c>
       <c r="I209" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J209" t="b">
         <v>1</v>
       </c>
       <c r="K209">
-        <v>66.17720451206469</v>
+        <v>66.13023562229581</v>
       </c>
       <c r="L209">
         <v>20.45869883040936</v>
@@ -12207,7 +12207,7 @@
         <v>16.07245691629453</v>
       </c>
       <c r="N209">
-        <v>66.17718665643571</v>
+        <v>23.44149865543357</v>
       </c>
       <c r="O209">
         <v>23.28590402691404</v>
@@ -12219,7 +12219,7 @@
         <v>27</v>
       </c>
       <c r="S209">
-        <v>-42.89130048515065</v>
+        <v>-42.84433159538177</v>
       </c>
     </row>
     <row r="210" spans="1:19">
@@ -12263,7 +12263,7 @@
         <v>21.25741213556917</v>
       </c>
       <c r="N210">
-        <v>21.038950683721</v>
+        <v>21.03892003378582</v>
       </c>
       <c r="O210">
         <v>21.03892003378581</v>
@@ -12319,7 +12319,7 @@
         <v>21.25741213556917</v>
       </c>
       <c r="N211">
-        <v>21.038950683721</v>
+        <v>21.03892003378582</v>
       </c>
       <c r="O211">
         <v>21.03892003378581</v>
@@ -12375,7 +12375,7 @@
         <v>21.25741213556917</v>
       </c>
       <c r="N212">
-        <v>21.038950683721</v>
+        <v>21.03892003378582</v>
       </c>
       <c r="O212">
         <v>21.03892003378581</v>
@@ -12387,7 +12387,7 @@
         <v>26</v>
       </c>
       <c r="S212">
-        <v>3.064993517598591E-05</v>
+        <v>-5.551115123125783E-15</v>
       </c>
     </row>
     <row r="213" spans="1:19">
@@ -12431,7 +12431,7 @@
         <v>21.25741213556917</v>
       </c>
       <c r="N213">
-        <v>21.038950683721</v>
+        <v>21.03892003378582</v>
       </c>
       <c r="O213">
         <v>21.03892003378581</v>
@@ -12487,7 +12487,7 @@
         <v>33.45738695423864</v>
       </c>
       <c r="N214">
-        <v>29.40835318500872</v>
+        <v>29.40824663502366</v>
       </c>
       <c r="O214">
         <v>29.40824663502351</v>
@@ -12543,7 +12543,7 @@
         <v>33.45738695423864</v>
       </c>
       <c r="N215">
-        <v>29.40835318500872</v>
+        <v>29.40824663502366</v>
       </c>
       <c r="O215">
         <v>29.40824663502351</v>
@@ -12599,7 +12599,7 @@
         <v>33.45738695423864</v>
       </c>
       <c r="N216">
-        <v>29.40835318500872</v>
+        <v>29.40824663502366</v>
       </c>
       <c r="O216">
         <v>29.40824663502351</v>
@@ -12611,7 +12611,7 @@
         <v>26</v>
       </c>
       <c r="S216">
-        <v>0.000106549985018356</v>
+        <v>-4.440892098500626E-14</v>
       </c>
     </row>
     <row r="217" spans="1:19">
@@ -12655,7 +12655,7 @@
         <v>33.45738695423864</v>
       </c>
       <c r="N217">
-        <v>29.40835318500872</v>
+        <v>29.40824663502366</v>
       </c>
       <c r="O217">
         <v>29.40824663502351</v>
@@ -12711,7 +12711,7 @@
         <v>49.50488865126464</v>
       </c>
       <c r="N218">
-        <v>61.13397144307567</v>
+        <v>61.13420156564051</v>
       </c>
       <c r="O218">
         <v>61.13420156564019</v>
@@ -12767,7 +12767,7 @@
         <v>49.50488865126464</v>
       </c>
       <c r="N219">
-        <v>61.13397144307567</v>
+        <v>61.13420156564051</v>
       </c>
       <c r="O219">
         <v>61.13420156564019</v>
@@ -12823,7 +12823,7 @@
         <v>49.50488865126464</v>
       </c>
       <c r="N220">
-        <v>61.13397144307567</v>
+        <v>61.13420156564051</v>
       </c>
       <c r="O220">
         <v>61.13420156564019</v>
@@ -12835,7 +12835,7 @@
         <v>26</v>
       </c>
       <c r="S220">
-        <v>-0.0002301225648260186</v>
+        <v>1.110223024625157E-14</v>
       </c>
     </row>
     <row r="221" spans="1:19">
@@ -12879,7 +12879,7 @@
         <v>49.50488865126464</v>
       </c>
       <c r="N221">
-        <v>61.13397144307567</v>
+        <v>61.13420156564051</v>
       </c>
       <c r="O221">
         <v>61.13420156564019</v>
@@ -12935,7 +12935,7 @@
         <v>23.51245921087659</v>
       </c>
       <c r="N222">
-        <v>23.36200165785082</v>
+        <v>23.36212016212885</v>
       </c>
       <c r="O222">
         <v>23.36212016212899</v>
@@ -12991,7 +12991,7 @@
         <v>23.51245921087659</v>
       </c>
       <c r="N223">
-        <v>23.36200165785082</v>
+        <v>23.36212016212885</v>
       </c>
       <c r="O223">
         <v>23.36212016212899</v>
@@ -13047,7 +13047,7 @@
         <v>23.51245921087659</v>
       </c>
       <c r="N224">
-        <v>23.36200165785082</v>
+        <v>23.36212016212885</v>
       </c>
       <c r="O224">
         <v>23.36212016212899</v>
@@ -13059,7 +13059,7 @@
         <v>26</v>
       </c>
       <c r="S224">
-        <v>-0.0001185042778961698</v>
+        <v>1.387778780781446E-13</v>
       </c>
     </row>
     <row r="225" spans="1:19">
@@ -13103,7 +13103,7 @@
         <v>23.51245921087659</v>
       </c>
       <c r="N225">
-        <v>23.36200165785082</v>
+        <v>23.36212016212885</v>
       </c>
       <c r="O225">
         <v>23.36212016212899</v>
@@ -13159,7 +13159,7 @@
         <v>97.17773718407359</v>
       </c>
       <c r="N226">
-        <v>88.08415428523584</v>
+        <v>88.08390437194763</v>
       </c>
       <c r="O226">
         <v>96.15271201484036</v>
@@ -13215,7 +13215,7 @@
         <v>97.17773718407359</v>
       </c>
       <c r="N227">
-        <v>88.08415428523584</v>
+        <v>88.08390437194763</v>
       </c>
       <c r="O227">
         <v>96.15271201484036</v>
@@ -13271,7 +13271,7 @@
         <v>97.17773718407359</v>
       </c>
       <c r="N228">
-        <v>88.08415428523584</v>
+        <v>88.08390437194763</v>
       </c>
       <c r="O228">
         <v>96.15271201484036</v>
@@ -13283,7 +13283,7 @@
         <v>26</v>
       </c>
       <c r="S228">
-        <v>0.0002499132882416433</v>
+        <v>3.33066907387547E-14</v>
       </c>
     </row>
     <row r="229" spans="1:19">
@@ -13327,7 +13327,7 @@
         <v>97.17773718407359</v>
       </c>
       <c r="N229">
-        <v>88.08415428523584</v>
+        <v>88.08390437194763</v>
       </c>
       <c r="O229">
         <v>96.15271201484036</v>
@@ -13383,7 +13383,7 @@
         <v>61.71375169524719</v>
       </c>
       <c r="N230">
-        <v>59.83277074675178</v>
+        <v>61.94837221944849</v>
       </c>
       <c r="O230">
         <v>61.81075895629139</v>
@@ -13439,7 +13439,7 @@
         <v>61.71375169524719</v>
       </c>
       <c r="N231">
-        <v>59.83277074675178</v>
+        <v>61.94837221944849</v>
       </c>
       <c r="O231">
         <v>61.81075895629139</v>
@@ -13495,7 +13495,7 @@
         <v>61.71375169524719</v>
       </c>
       <c r="N232">
-        <v>59.83277074675178</v>
+        <v>61.94837221944849</v>
       </c>
       <c r="O232">
         <v>61.81075895629139</v>
@@ -13507,7 +13507,7 @@
         <v>26</v>
       </c>
       <c r="S232">
-        <v>0.0502683368828527</v>
+        <v>2.165869809579557</v>
       </c>
     </row>
     <row r="233" spans="1:19">
@@ -13551,7 +13551,7 @@
         <v>61.71375169524719</v>
       </c>
       <c r="N233">
-        <v>59.83277074675178</v>
+        <v>61.94837221944849</v>
       </c>
       <c r="O233">
         <v>61.81075895629139</v>
@@ -13607,7 +13607,7 @@
         <v>51.45661523940287</v>
       </c>
       <c r="N234">
-        <v>51.98171191214285</v>
+        <v>51.98194203929357</v>
       </c>
       <c r="O234">
         <v>52.98554620399702</v>
@@ -13663,7 +13663,7 @@
         <v>51.45661523940287</v>
       </c>
       <c r="N235">
-        <v>51.98171191214285</v>
+        <v>51.98194203929357</v>
       </c>
       <c r="O235">
         <v>52.98554620399702</v>
@@ -13719,7 +13719,7 @@
         <v>51.45661523940287</v>
       </c>
       <c r="N236">
-        <v>51.98171191214285</v>
+        <v>51.98194203929357</v>
       </c>
       <c r="O236">
         <v>52.98554620399702</v>
@@ -13731,7 +13731,7 @@
         <v>26</v>
       </c>
       <c r="S236">
-        <v>-0.0002301271504578928</v>
+        <v>2.664535259100376E-13</v>
       </c>
     </row>
     <row r="237" spans="1:19">
@@ -13775,7 +13775,7 @@
         <v>51.45661523940287</v>
       </c>
       <c r="N237">
-        <v>51.98171191214285</v>
+        <v>51.98194203929357</v>
       </c>
       <c r="O237">
         <v>52.98554620399702</v>
@@ -13831,7 +13831,7 @@
         <v>93.2190249300493</v>
       </c>
       <c r="N238">
-        <v>88.62053914733956</v>
+        <v>88.62047920240059</v>
       </c>
       <c r="O238">
         <v>92.15936562501972</v>
@@ -13887,7 +13887,7 @@
         <v>93.2190249300493</v>
       </c>
       <c r="N239">
-        <v>88.62053914733956</v>
+        <v>88.62047920240059</v>
       </c>
       <c r="O239">
         <v>92.15936562501972</v>
@@ -13943,7 +13943,7 @@
         <v>93.2190249300493</v>
       </c>
       <c r="N240">
-        <v>88.62053914733956</v>
+        <v>88.62047920240059</v>
       </c>
       <c r="O240">
         <v>92.15936562501972</v>
@@ -13955,7 +13955,7 @@
         <v>26</v>
       </c>
       <c r="S240">
-        <v>5.994493899041942E-05</v>
+        <v>1.110223024625157E-14</v>
       </c>
     </row>
     <row r="241" spans="1:19">
@@ -13999,7 +13999,7 @@
         <v>93.2190249300493</v>
       </c>
       <c r="N241">
-        <v>88.62053914733956</v>
+        <v>88.62047920240059</v>
       </c>
       <c r="O241">
         <v>92.15936562501972</v>
@@ -14055,7 +14055,7 @@
         <v>89.00552654641174</v>
       </c>
       <c r="N242">
-        <v>91.6109852243535</v>
+        <v>91.61098668710525</v>
       </c>
       <c r="O242">
         <v>88.26633420980771</v>
@@ -14111,7 +14111,7 @@
         <v>89.00552654641174</v>
       </c>
       <c r="N243">
-        <v>91.6109852243535</v>
+        <v>91.61098668710525</v>
       </c>
       <c r="O243">
         <v>88.26633420980771</v>
@@ -14167,7 +14167,7 @@
         <v>89.00552654641174</v>
       </c>
       <c r="N244">
-        <v>91.6109852243535</v>
+        <v>91.61098668710525</v>
       </c>
       <c r="O244">
         <v>88.26633420980771</v>
@@ -14179,7 +14179,7 @@
         <v>26</v>
       </c>
       <c r="S244">
-        <v>-1.462751664238482E-06</v>
+        <v>9.992007221626409E-14</v>
       </c>
     </row>
     <row r="245" spans="1:19">
@@ -14223,7 +14223,7 @@
         <v>89.00552654641174</v>
       </c>
       <c r="N245">
-        <v>91.6109852243535</v>
+        <v>91.61098668710525</v>
       </c>
       <c r="O245">
         <v>88.26633420980771</v>
@@ -14258,13 +14258,13 @@
         <v>46</v>
       </c>
       <c r="G246" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H246" t="b">
         <v>0</v>
       </c>
       <c r="I246" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J246" t="b">
         <v>1</v>
@@ -14279,7 +14279,7 @@
         <v>76.7437740434725</v>
       </c>
       <c r="N246">
-        <v>78.97644453606041</v>
+        <v>75.26921795348109</v>
       </c>
       <c r="O246">
         <v>75.81904163627176</v>
@@ -14314,13 +14314,13 @@
         <v>46</v>
       </c>
       <c r="G247" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H247" t="b">
         <v>0</v>
       </c>
       <c r="I247" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J247" t="b">
         <v>1</v>
@@ -14335,7 +14335,7 @@
         <v>76.7437740434725</v>
       </c>
       <c r="N247">
-        <v>78.97644453606041</v>
+        <v>75.26921795348109</v>
       </c>
       <c r="O247">
         <v>75.81904163627176</v>
@@ -14370,13 +14370,13 @@
         <v>46</v>
       </c>
       <c r="G248" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H248" t="b">
         <v>0</v>
       </c>
       <c r="I248" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J248" t="b">
         <v>1</v>
@@ -14391,7 +14391,7 @@
         <v>76.7437740434725</v>
       </c>
       <c r="N248">
-        <v>78.97644453606041</v>
+        <v>75.26921795348109</v>
       </c>
       <c r="O248">
         <v>75.81904163627176</v>
@@ -14403,7 +14403,7 @@
         <v>26</v>
       </c>
       <c r="S248">
-        <v>-5.968713634452172E-06</v>
+        <v>-3.707232551292972</v>
       </c>
     </row>
     <row r="249" spans="1:19">
@@ -14426,13 +14426,13 @@
         <v>46</v>
       </c>
       <c r="G249" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H249" t="b">
         <v>0</v>
       </c>
       <c r="I249" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J249" t="b">
         <v>1</v>
@@ -14447,7 +14447,7 @@
         <v>76.7437740434725</v>
       </c>
       <c r="N249">
-        <v>78.97644453606041</v>
+        <v>75.26921795348109</v>
       </c>
       <c r="O249">
         <v>75.81904163627176</v>
@@ -14482,19 +14482,19 @@
         <v>46</v>
       </c>
       <c r="G250" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H250" t="b">
         <v>0</v>
       </c>
       <c r="I250" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J250" t="b">
         <v>1</v>
       </c>
       <c r="K250">
-        <v>55.44014421776925</v>
+        <v>55.4603219525063</v>
       </c>
       <c r="L250">
         <v>92.41490820524366</v>
@@ -14503,7 +14503,7 @@
         <v>93.45955547116742</v>
       </c>
       <c r="N250">
-        <v>55.44161423316025</v>
+        <v>91.85730646326206</v>
       </c>
       <c r="O250">
         <v>92.00733593091454</v>
@@ -14515,7 +14515,7 @@
         <v>24</v>
       </c>
       <c r="S250">
-        <v>36.97476398747441</v>
+        <v>36.95458625273736</v>
       </c>
     </row>
     <row r="251" spans="1:19">
@@ -14538,19 +14538,19 @@
         <v>46</v>
       </c>
       <c r="G251" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H251" t="b">
         <v>0</v>
       </c>
       <c r="I251" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J251" t="b">
         <v>1</v>
       </c>
       <c r="K251">
-        <v>55.44014421776925</v>
+        <v>55.4603219525063</v>
       </c>
       <c r="L251">
         <v>92.41490820524366</v>
@@ -14559,7 +14559,7 @@
         <v>93.45955547116742</v>
       </c>
       <c r="N251">
-        <v>55.44161423316025</v>
+        <v>91.85730646326206</v>
       </c>
       <c r="O251">
         <v>92.00733593091454</v>
@@ -14571,7 +14571,7 @@
         <v>25</v>
       </c>
       <c r="S251">
-        <v>38.01941125339818</v>
+        <v>37.99923351866112</v>
       </c>
     </row>
     <row r="252" spans="1:19">
@@ -14594,19 +14594,19 @@
         <v>46</v>
       </c>
       <c r="G252" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H252" t="b">
         <v>0</v>
       </c>
       <c r="I252" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J252" t="b">
         <v>1</v>
       </c>
       <c r="K252">
-        <v>55.44014421776925</v>
+        <v>55.4603219525063</v>
       </c>
       <c r="L252">
         <v>92.41490820524366</v>
@@ -14615,7 +14615,7 @@
         <v>93.45955547116742</v>
       </c>
       <c r="N252">
-        <v>55.44161423316025</v>
+        <v>91.85730646326206</v>
       </c>
       <c r="O252">
         <v>92.00733593091454</v>
@@ -14627,7 +14627,7 @@
         <v>26</v>
       </c>
       <c r="S252">
-        <v>0.001470015391002999</v>
+        <v>36.39698451075576</v>
       </c>
     </row>
     <row r="253" spans="1:19">
@@ -14650,19 +14650,19 @@
         <v>46</v>
       </c>
       <c r="G253" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H253" t="b">
         <v>0</v>
       </c>
       <c r="I253" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J253" t="b">
         <v>1</v>
       </c>
       <c r="K253">
-        <v>55.44014421776925</v>
+        <v>55.4603219525063</v>
       </c>
       <c r="L253">
         <v>92.41490820524366</v>
@@ -14671,7 +14671,7 @@
         <v>93.45955547116742</v>
       </c>
       <c r="N253">
-        <v>55.44161423316025</v>
+        <v>91.85730646326206</v>
       </c>
       <c r="O253">
         <v>92.00733593091454</v>
@@ -14683,7 +14683,7 @@
         <v>27</v>
       </c>
       <c r="S253">
-        <v>36.56719171314528</v>
+        <v>36.54701397840824</v>
       </c>
     </row>
     <row r="254" spans="1:19">
@@ -14727,7 +14727,7 @@
         <v>21.04725995974015</v>
       </c>
       <c r="N254">
-        <v>20.88994010277126</v>
+        <v>20.88991652567136</v>
       </c>
       <c r="O254">
         <v>20.8899165256715</v>
@@ -14783,7 +14783,7 @@
         <v>21.04725995974015</v>
       </c>
       <c r="N255">
-        <v>20.88994010277126</v>
+        <v>20.88991652567136</v>
       </c>
       <c r="O255">
         <v>20.8899165256715</v>
@@ -14839,7 +14839,7 @@
         <v>21.04725995974015</v>
       </c>
       <c r="N256">
-        <v>20.88994010277126</v>
+        <v>20.88991652567136</v>
       </c>
       <c r="O256">
         <v>20.8899165256715</v>
@@ -14851,7 +14851,7 @@
         <v>26</v>
       </c>
       <c r="S256">
-        <v>2.35770997614182E-05</v>
+        <v>-1.27675647831893E-13</v>
       </c>
     </row>
     <row r="257" spans="1:19">
@@ -14895,7 +14895,7 @@
         <v>21.04725995974015</v>
       </c>
       <c r="N257">
-        <v>20.88994010277126</v>
+        <v>20.88991652567136</v>
       </c>
       <c r="O257">
         <v>20.8899165256715</v>
@@ -14951,7 +14951,7 @@
         <v>29.08838937506049</v>
       </c>
       <c r="N258">
-        <v>29.08451496090197</v>
+        <v>29.08416921339025</v>
       </c>
       <c r="O258">
         <v>29.08416921339023</v>
@@ -15007,7 +15007,7 @@
         <v>29.08838937506049</v>
       </c>
       <c r="N259">
-        <v>29.08451496090197</v>
+        <v>29.08416921339025</v>
       </c>
       <c r="O259">
         <v>29.08416921339023</v>
@@ -15063,7 +15063,7 @@
         <v>29.08838937506049</v>
       </c>
       <c r="N260">
-        <v>29.08451496090197</v>
+        <v>29.08416921339025</v>
       </c>
       <c r="O260">
         <v>29.08416921339023</v>
@@ -15075,7 +15075,7 @@
         <v>26</v>
       </c>
       <c r="S260">
-        <v>0.0003457475115320463</v>
+        <v>-1.942890293094024E-13</v>
       </c>
     </row>
     <row r="261" spans="1:19">
@@ -15119,7 +15119,7 @@
         <v>29.08838937506049</v>
       </c>
       <c r="N261">
-        <v>29.08451496090197</v>
+        <v>29.08416921339025</v>
       </c>
       <c r="O261">
         <v>29.08416921339023</v>
@@ -15175,7 +15175,7 @@
         <v>48.73887699571039</v>
       </c>
       <c r="N262">
-        <v>61.7447773926749</v>
+        <v>61.74569966247251</v>
       </c>
       <c r="O262">
         <v>61.7456996624733</v>
@@ -15231,7 +15231,7 @@
         <v>48.73887699571039</v>
       </c>
       <c r="N263">
-        <v>61.7447773926749</v>
+        <v>61.74569966247251</v>
       </c>
       <c r="O263">
         <v>61.7456996624733</v>
@@ -15287,7 +15287,7 @@
         <v>48.73887699571039</v>
       </c>
       <c r="N264">
-        <v>61.7447773926749</v>
+        <v>61.74569966247251</v>
       </c>
       <c r="O264">
         <v>61.7456996624733</v>
@@ -15299,7 +15299,7 @@
         <v>26</v>
       </c>
       <c r="S264">
-        <v>-0.0009222697986310813</v>
+        <v>-1.021405182655144E-12</v>
       </c>
     </row>
     <row r="265" spans="1:19">
@@ -15343,7 +15343,7 @@
         <v>48.73887699571039</v>
       </c>
       <c r="N265">
-        <v>61.7447773926749</v>
+        <v>61.74569966247251</v>
       </c>
       <c r="O265">
         <v>61.7456996624733</v>
@@ -15399,7 +15399,7 @@
         <v>23.65268017148865</v>
       </c>
       <c r="N266">
-        <v>23.9161785491866</v>
+        <v>23.91662622988867</v>
       </c>
       <c r="O266">
         <v>23.9166262298883</v>
@@ -15455,7 +15455,7 @@
         <v>23.65268017148865</v>
       </c>
       <c r="N267">
-        <v>23.9161785491866</v>
+        <v>23.91662622988867</v>
       </c>
       <c r="O267">
         <v>23.9166262298883</v>
@@ -15511,7 +15511,7 @@
         <v>23.65268017148865</v>
       </c>
       <c r="N268">
-        <v>23.9161785491866</v>
+        <v>23.91662622988867</v>
       </c>
       <c r="O268">
         <v>23.9166262298883</v>
@@ -15523,7 +15523,7 @@
         <v>26</v>
       </c>
       <c r="S268">
-        <v>-0.0004476807021536189</v>
+        <v>-8.881784197001252E-14</v>
       </c>
     </row>
     <row r="269" spans="1:19">
@@ -15567,7 +15567,7 @@
         <v>23.65268017148865</v>
       </c>
       <c r="N269">
-        <v>23.9161785491866</v>
+        <v>23.91662622988867</v>
       </c>
       <c r="O269">
         <v>23.9166262298883</v>
@@ -15623,7 +15623,7 @@
         <v>96.81338803267714</v>
       </c>
       <c r="N270">
-        <v>87.37241516290105</v>
+        <v>87.370478753988</v>
       </c>
       <c r="O270">
         <v>96.61527149669007</v>
@@ -15679,7 +15679,7 @@
         <v>96.81338803267714</v>
       </c>
       <c r="N271">
-        <v>87.37241516290105</v>
+        <v>87.370478753988</v>
       </c>
       <c r="O271">
         <v>96.61527149669007</v>
@@ -15735,7 +15735,7 @@
         <v>96.81338803267714</v>
       </c>
       <c r="N272">
-        <v>87.37241516290105</v>
+        <v>87.370478753988</v>
       </c>
       <c r="O272">
         <v>96.61527149669007</v>
@@ -15747,7 +15747,7 @@
         <v>26</v>
       </c>
       <c r="S272">
-        <v>0.0019364089128171</v>
+        <v>-2.442490654175344E-13</v>
       </c>
     </row>
     <row r="273" spans="1:19">
@@ -15791,7 +15791,7 @@
         <v>96.81338803267714</v>
       </c>
       <c r="N273">
-        <v>87.37241516290105</v>
+        <v>87.370478753988</v>
       </c>
       <c r="O273">
         <v>96.61527149669007</v>
@@ -15847,7 +15847,7 @@
         <v>51.28828380312933</v>
       </c>
       <c r="N274">
-        <v>51.94889999927202</v>
+        <v>51.94822224461548</v>
       </c>
       <c r="O274">
         <v>54.78359986350526</v>
@@ -15903,7 +15903,7 @@
         <v>51.28828380312933</v>
       </c>
       <c r="N275">
-        <v>51.94889999927202</v>
+        <v>51.94822224461548</v>
       </c>
       <c r="O275">
         <v>54.78359986350526</v>
@@ -15959,7 +15959,7 @@
         <v>51.28828380312933</v>
       </c>
       <c r="N276">
-        <v>51.94889999927202</v>
+        <v>51.94822224461548</v>
       </c>
       <c r="O276">
         <v>54.78359986350526</v>
@@ -15971,7 +15971,7 @@
         <v>26</v>
       </c>
       <c r="S276">
-        <v>0.000677754656286389</v>
+        <v>-2.442490654175344E-13</v>
       </c>
     </row>
     <row r="277" spans="1:19">
@@ -16015,7 +16015,7 @@
         <v>51.28828380312933</v>
       </c>
       <c r="N277">
-        <v>51.94889999927202</v>
+        <v>51.94822224461548</v>
       </c>
       <c r="O277">
         <v>54.78359986350526</v>
@@ -16071,7 +16071,7 @@
         <v>94.03133607433651</v>
       </c>
       <c r="N278">
-        <v>88.81734391689325</v>
+        <v>88.81688255591106</v>
       </c>
       <c r="O278">
         <v>92.98122335219247</v>
@@ -16127,7 +16127,7 @@
         <v>94.03133607433651</v>
       </c>
       <c r="N279">
-        <v>88.81734391689325</v>
+        <v>88.81688255591106</v>
       </c>
       <c r="O279">
         <v>92.98122335219247</v>
@@ -16183,7 +16183,7 @@
         <v>94.03133607433651</v>
       </c>
       <c r="N280">
-        <v>88.81734391689325</v>
+        <v>88.81688255591106</v>
       </c>
       <c r="O280">
         <v>92.98122335219247</v>
@@ -16195,7 +16195,7 @@
         <v>26</v>
       </c>
       <c r="S280">
-        <v>0.0004613609821402243</v>
+        <v>-5.551115123125783E-14</v>
       </c>
     </row>
     <row r="281" spans="1:19">
@@ -16239,7 +16239,7 @@
         <v>94.03133607433651</v>
       </c>
       <c r="N281">
-        <v>88.81734391689325</v>
+        <v>88.81688255591106</v>
       </c>
       <c r="O281">
         <v>92.98122335219247</v>
@@ -16295,7 +16295,7 @@
         <v>89.59600768057201</v>
       </c>
       <c r="N282">
-        <v>92.0254513940278</v>
+        <v>92.02554441496301</v>
       </c>
       <c r="O282">
         <v>88.62246431716979</v>
@@ -16351,7 +16351,7 @@
         <v>89.59600768057201</v>
       </c>
       <c r="N283">
-        <v>92.0254513940278</v>
+        <v>92.02554441496301</v>
       </c>
       <c r="O283">
         <v>88.62246431716979</v>
@@ -16407,7 +16407,7 @@
         <v>89.59600768057201</v>
       </c>
       <c r="N284">
-        <v>92.0254513940278</v>
+        <v>92.02554441496301</v>
       </c>
       <c r="O284">
         <v>88.62246431716979</v>
@@ -16419,7 +16419,7 @@
         <v>26</v>
       </c>
       <c r="S284">
-        <v>-9.302093518792631E-05</v>
+        <v>1.110223024625157E-14</v>
       </c>
     </row>
     <row r="285" spans="1:19">
@@ -16463,7 +16463,7 @@
         <v>89.59600768057201</v>
       </c>
       <c r="N285">
-        <v>92.0254513940278</v>
+        <v>92.02554441496301</v>
       </c>
       <c r="O285">
         <v>88.62246431716979</v>
@@ -16498,13 +16498,13 @@
         <v>46</v>
       </c>
       <c r="G286" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H286" t="b">
         <v>0</v>
       </c>
       <c r="I286" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J286" t="b">
         <v>1</v>
@@ -16519,7 +16519,7 @@
         <v>74.44156432090232</v>
       </c>
       <c r="N286">
-        <v>76.75134240346767</v>
+        <v>73.55704277011885</v>
       </c>
       <c r="O286">
         <v>74.16403417043581</v>
@@ -16554,13 +16554,13 @@
         <v>46</v>
       </c>
       <c r="G287" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H287" t="b">
         <v>0</v>
       </c>
       <c r="I287" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J287" t="b">
         <v>1</v>
@@ -16575,7 +16575,7 @@
         <v>74.44156432090232</v>
       </c>
       <c r="N287">
-        <v>76.75134240346767</v>
+        <v>73.55704277011885</v>
       </c>
       <c r="O287">
         <v>74.16403417043581</v>
@@ -16610,13 +16610,13 @@
         <v>46</v>
       </c>
       <c r="G288" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H288" t="b">
         <v>0</v>
       </c>
       <c r="I288" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J288" t="b">
         <v>1</v>
@@ -16631,7 +16631,7 @@
         <v>74.44156432090232</v>
       </c>
       <c r="N288">
-        <v>76.75134240346767</v>
+        <v>73.55704277011885</v>
       </c>
       <c r="O288">
         <v>74.16403417043581</v>
@@ -16643,7 +16643,7 @@
         <v>26</v>
       </c>
       <c r="S288">
-        <v>9.920268743135452E-05</v>
+        <v>-3.194200430661398</v>
       </c>
     </row>
     <row r="289" spans="1:19">
@@ -16666,13 +16666,13 @@
         <v>46</v>
       </c>
       <c r="G289" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H289" t="b">
         <v>0</v>
       </c>
       <c r="I289" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J289" t="b">
         <v>1</v>
@@ -16687,7 +16687,7 @@
         <v>74.44156432090232</v>
       </c>
       <c r="N289">
-        <v>76.75134240346767</v>
+        <v>73.55704277011885</v>
       </c>
       <c r="O289">
         <v>74.16403417043581</v>
@@ -16722,19 +16722,19 @@
         <v>46</v>
       </c>
       <c r="G290" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H290" t="b">
         <v>0</v>
       </c>
       <c r="I290" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J290" t="b">
         <v>1</v>
       </c>
       <c r="K290">
-        <v>53.64300101889923</v>
+        <v>53.31034912579611</v>
       </c>
       <c r="L290">
         <v>11.78252784220314</v>
@@ -16743,7 +16743,7 @@
         <v>16.02529247027256</v>
       </c>
       <c r="N290">
-        <v>53.64017208513795</v>
+        <v>11.48115825434971</v>
       </c>
       <c r="O290">
         <v>11.76849713904182</v>
@@ -16755,7 +16755,7 @@
         <v>24</v>
       </c>
       <c r="S290">
-        <v>-41.86047317669609</v>
+        <v>-41.52782128359297</v>
       </c>
     </row>
     <row r="291" spans="1:19">
@@ -16778,19 +16778,19 @@
         <v>46</v>
       </c>
       <c r="G291" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H291" t="b">
         <v>0</v>
       </c>
       <c r="I291" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J291" t="b">
         <v>1</v>
       </c>
       <c r="K291">
-        <v>53.64300101889923</v>
+        <v>53.31034912579611</v>
       </c>
       <c r="L291">
         <v>11.78252784220314</v>
@@ -16799,7 +16799,7 @@
         <v>16.02529247027256</v>
       </c>
       <c r="N291">
-        <v>53.64017208513795</v>
+        <v>11.48115825434971</v>
       </c>
       <c r="O291">
         <v>11.76849713904182</v>
@@ -16811,7 +16811,7 @@
         <v>25</v>
       </c>
       <c r="S291">
-        <v>-37.61770854862667</v>
+        <v>-37.28505665552355</v>
       </c>
     </row>
     <row r="292" spans="1:19">
@@ -16834,19 +16834,19 @@
         <v>46</v>
       </c>
       <c r="G292" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H292" t="b">
         <v>0</v>
       </c>
       <c r="I292" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J292" t="b">
         <v>1</v>
       </c>
       <c r="K292">
-        <v>53.64300101889923</v>
+        <v>53.31034912579611</v>
       </c>
       <c r="L292">
         <v>11.78252784220314</v>
@@ -16855,7 +16855,7 @@
         <v>16.02529247027256</v>
       </c>
       <c r="N292">
-        <v>53.64017208513795</v>
+        <v>11.48115825434971</v>
       </c>
       <c r="O292">
         <v>11.76849713904182</v>
@@ -16867,7 +16867,7 @@
         <v>26</v>
       </c>
       <c r="S292">
-        <v>-0.002828933761278574</v>
+        <v>-41.8291908714464</v>
       </c>
     </row>
     <row r="293" spans="1:19">
@@ -16890,19 +16890,19 @@
         <v>46</v>
       </c>
       <c r="G293" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H293" t="b">
         <v>0</v>
       </c>
       <c r="I293" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J293" t="b">
         <v>1</v>
       </c>
       <c r="K293">
-        <v>53.64300101889923</v>
+        <v>53.31034912579611</v>
       </c>
       <c r="L293">
         <v>11.78252784220314</v>
@@ -16911,7 +16911,7 @@
         <v>16.02529247027256</v>
       </c>
       <c r="N293">
-        <v>53.64017208513795</v>
+        <v>11.48115825434971</v>
       </c>
       <c r="O293">
         <v>11.76849713904182</v>
@@ -16923,7 +16923,7 @@
         <v>27</v>
       </c>
       <c r="S293">
-        <v>-41.87450387985741</v>
+        <v>-41.54185198675429</v>
       </c>
     </row>
     <row r="294" spans="1:19">
@@ -16967,7 +16967,7 @@
         <v>20.76722279995309</v>
       </c>
       <c r="N294">
-        <v>20.46367109769706</v>
+        <v>20.44825700998217</v>
       </c>
       <c r="O294">
         <v>20.44825700998185</v>
@@ -17023,7 +17023,7 @@
         <v>20.76722279995309</v>
       </c>
       <c r="N295">
-        <v>20.46367109769706</v>
+        <v>20.44825700998217</v>
       </c>
       <c r="O295">
         <v>20.44825700998185</v>
@@ -17079,7 +17079,7 @@
         <v>20.76722279995309</v>
       </c>
       <c r="N296">
-        <v>20.46367109769706</v>
+        <v>20.44825700998217</v>
       </c>
       <c r="O296">
         <v>20.44825700998185</v>
@@ -17091,7 +17091,7 @@
         <v>26</v>
       </c>
       <c r="S296">
-        <v>0.0154140877152098</v>
+        <v>3.191891195797325E-13</v>
       </c>
     </row>
     <row r="297" spans="1:19">
@@ -17135,7 +17135,7 @@
         <v>20.76722279995309</v>
       </c>
       <c r="N297">
-        <v>20.46367109769706</v>
+        <v>20.44825700998217</v>
       </c>
       <c r="O297">
         <v>20.44825700998185</v>
@@ -17191,7 +17191,7 @@
         <v>29.60818377641896</v>
       </c>
       <c r="N298">
-        <v>28.58114103347858</v>
+        <v>28.56363375290934</v>
       </c>
       <c r="O298">
         <v>28.56364349950626</v>
@@ -17247,7 +17247,7 @@
         <v>29.60818377641896</v>
       </c>
       <c r="N299">
-        <v>28.58114103347858</v>
+        <v>28.56363375290934</v>
       </c>
       <c r="O299">
         <v>28.56364349950626</v>
@@ -17303,7 +17303,7 @@
         <v>29.60818377641896</v>
       </c>
       <c r="N300">
-        <v>28.58114103347858</v>
+        <v>28.56363375290934</v>
       </c>
       <c r="O300">
         <v>28.56364349950626</v>
@@ -17315,7 +17315,7 @@
         <v>26</v>
       </c>
       <c r="S300">
-        <v>0.01749753397061182</v>
+        <v>-9.746598633730841E-06</v>
       </c>
     </row>
     <row r="301" spans="1:19">
@@ -17359,7 +17359,7 @@
         <v>29.60818377641896</v>
       </c>
       <c r="N301">
-        <v>28.58114103347858</v>
+        <v>28.56363375290934</v>
       </c>
       <c r="O301">
         <v>28.56364349950626</v>
@@ -17415,7 +17415,7 @@
         <v>45.41033977823029</v>
       </c>
       <c r="N302">
-        <v>57.96575148629909</v>
+        <v>58.01083233523558</v>
       </c>
       <c r="O302">
         <v>58.0108328128624</v>
@@ -17471,7 +17471,7 @@
         <v>45.41033977823029</v>
       </c>
       <c r="N303">
-        <v>57.96575148629909</v>
+        <v>58.01083233523558</v>
       </c>
       <c r="O303">
         <v>58.0108328128624</v>
@@ -17527,7 +17527,7 @@
         <v>45.41033977823029</v>
       </c>
       <c r="N304">
-        <v>57.96575148629909</v>
+        <v>58.01083233523558</v>
       </c>
       <c r="O304">
         <v>58.0108328128624</v>
@@ -17539,7 +17539,7 @@
         <v>26</v>
       </c>
       <c r="S304">
-        <v>-0.04508132656672048</v>
+        <v>-4.776302242603947E-07</v>
       </c>
     </row>
     <row r="305" spans="1:19">
@@ -17583,7 +17583,7 @@
         <v>45.41033977823029</v>
       </c>
       <c r="N305">
-        <v>57.96575148629909</v>
+        <v>58.01083233523558</v>
       </c>
       <c r="O305">
         <v>58.0108328128624</v>
@@ -17639,7 +17639,7 @@
         <v>22.92496016495961</v>
       </c>
       <c r="N306">
-        <v>24.26236009446145</v>
+        <v>24.30807926381246</v>
       </c>
       <c r="O306">
         <v>24.30807920702813</v>
@@ -17695,7 +17695,7 @@
         <v>22.92496016495961</v>
       </c>
       <c r="N307">
-        <v>24.26236009446145</v>
+        <v>24.30807926381246</v>
       </c>
       <c r="O307">
         <v>24.30807920702813</v>
@@ -17751,7 +17751,7 @@
         <v>22.92496016495961</v>
       </c>
       <c r="N308">
-        <v>24.26236009446145</v>
+        <v>24.30807926381246</v>
       </c>
       <c r="O308">
         <v>24.30807920702813</v>
@@ -17763,7 +17763,7 @@
         <v>26</v>
       </c>
       <c r="S308">
-        <v>-0.04571911256638361</v>
+        <v>5.678461867386631E-08</v>
       </c>
     </row>
     <row r="309" spans="1:19">
@@ -17807,7 +17807,7 @@
         <v>22.92496016495961</v>
       </c>
       <c r="N309">
-        <v>24.26236009446145</v>
+        <v>24.30807926381246</v>
       </c>
       <c r="O309">
         <v>24.30807920702813</v>
@@ -17863,7 +17863,7 @@
         <v>96.74972921398198</v>
       </c>
       <c r="N310">
-        <v>86.7674770249384</v>
+        <v>86.62347008600933</v>
       </c>
       <c r="O310">
         <v>96.83662791301964</v>
@@ -17919,7 +17919,7 @@
         <v>96.74972921398198</v>
       </c>
       <c r="N311">
-        <v>86.7674770249384</v>
+        <v>86.62347008600933</v>
       </c>
       <c r="O311">
         <v>96.83662791301964</v>
@@ -17975,7 +17975,7 @@
         <v>96.74972921398198</v>
       </c>
       <c r="N312">
-        <v>86.7674770249384</v>
+        <v>86.62347008600933</v>
       </c>
       <c r="O312">
         <v>96.83662791301964</v>
@@ -17987,7 +17987,7 @@
         <v>26</v>
       </c>
       <c r="S312">
-        <v>0.1440114783686219</v>
+        <v>4.539439557582625E-06</v>
       </c>
     </row>
     <row r="313" spans="1:19">
@@ -18031,7 +18031,7 @@
         <v>96.74972921398198</v>
       </c>
       <c r="N313">
-        <v>86.7674770249384</v>
+        <v>86.62347008600933</v>
       </c>
       <c r="O313">
         <v>96.83662791301964</v>
@@ -18066,13 +18066,13 @@
         <v>46</v>
       </c>
       <c r="G314" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H314" t="b">
         <v>0</v>
       </c>
       <c r="I314" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J314" t="b">
         <v>1</v>
@@ -18087,7 +18087,7 @@
         <v>61.26631725023351</v>
       </c>
       <c r="N314">
-        <v>59.835612024819</v>
+        <v>60.59917463655709</v>
       </c>
       <c r="O314">
         <v>60.62328032993742</v>
@@ -18122,13 +18122,13 @@
         <v>46</v>
       </c>
       <c r="G315" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H315" t="b">
         <v>0</v>
       </c>
       <c r="I315" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J315" t="b">
         <v>1</v>
@@ -18143,7 +18143,7 @@
         <v>61.26631725023351</v>
       </c>
       <c r="N315">
-        <v>59.835612024819</v>
+        <v>60.59917463655709</v>
       </c>
       <c r="O315">
         <v>60.62328032993742</v>
@@ -18178,13 +18178,13 @@
         <v>46</v>
       </c>
       <c r="G316" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H316" t="b">
         <v>0</v>
       </c>
       <c r="I316" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J316" t="b">
         <v>1</v>
@@ -18199,7 +18199,7 @@
         <v>61.26631725023351</v>
       </c>
       <c r="N316">
-        <v>59.835612024819</v>
+        <v>60.59917463655709</v>
       </c>
       <c r="O316">
         <v>60.62328032993742</v>
@@ -18211,7 +18211,7 @@
         <v>26</v>
       </c>
       <c r="S316">
-        <v>0.03994347292466394</v>
+        <v>0.803506084662764</v>
       </c>
     </row>
     <row r="317" spans="1:19">
@@ -18234,13 +18234,13 @@
         <v>46</v>
       </c>
       <c r="G317" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H317" t="b">
         <v>0</v>
       </c>
       <c r="I317" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J317" t="b">
         <v>1</v>
@@ -18255,7 +18255,7 @@
         <v>61.26631725023351</v>
       </c>
       <c r="N317">
-        <v>59.835612024819</v>
+        <v>60.59917463655709</v>
       </c>
       <c r="O317">
         <v>60.62328032993742</v>
@@ -18311,7 +18311,7 @@
         <v>51.33905338101908</v>
       </c>
       <c r="N318">
-        <v>51.87832534795208</v>
+        <v>51.8651703914626</v>
       </c>
       <c r="O318">
         <v>55.1021165348436</v>
@@ -18367,7 +18367,7 @@
         <v>51.33905338101908</v>
       </c>
       <c r="N319">
-        <v>51.87832534795208</v>
+        <v>51.8651703914626</v>
       </c>
       <c r="O319">
         <v>55.1021165348436</v>
@@ -18423,7 +18423,7 @@
         <v>51.33905338101908</v>
       </c>
       <c r="N320">
-        <v>51.87832534795208</v>
+        <v>51.8651703914626</v>
       </c>
       <c r="O320">
         <v>55.1021165348436</v>
@@ -18435,7 +18435,7 @@
         <v>26</v>
       </c>
       <c r="S320">
-        <v>0.01316071383007378</v>
+        <v>5.75734059315991E-06</v>
       </c>
     </row>
     <row r="321" spans="1:19">
@@ -18479,7 +18479,7 @@
         <v>51.33905338101908</v>
       </c>
       <c r="N321">
-        <v>51.87832534795208</v>
+        <v>51.8651703914626</v>
       </c>
       <c r="O321">
         <v>55.1021165348436</v>
@@ -18535,7 +18535,7 @@
         <v>94.0136234526498</v>
       </c>
       <c r="N322">
-        <v>88.61323762786944</v>
+        <v>88.59904659197406</v>
       </c>
       <c r="O322">
         <v>92.78607739506651</v>
@@ -18591,7 +18591,7 @@
         <v>94.0136234526498</v>
       </c>
       <c r="N323">
-        <v>88.61323762786944</v>
+        <v>88.59904659197406</v>
       </c>
       <c r="O323">
         <v>92.78607739506651</v>
@@ -18647,7 +18647,7 @@
         <v>94.0136234526498</v>
       </c>
       <c r="N324">
-        <v>88.61323762786944</v>
+        <v>88.59904659197406</v>
       </c>
       <c r="O324">
         <v>92.78607739506651</v>
@@ -18659,7 +18659,7 @@
         <v>26</v>
       </c>
       <c r="S324">
-        <v>0.01418960637633582</v>
+        <v>-1.4295190364777E-06</v>
       </c>
     </row>
     <row r="325" spans="1:19">
@@ -18703,7 +18703,7 @@
         <v>94.0136234526498</v>
       </c>
       <c r="N325">
-        <v>88.61323762786944</v>
+        <v>88.59904659197406</v>
       </c>
       <c r="O325">
         <v>92.78607739506651</v>
@@ -18759,7 +18759,7 @@
         <v>89.87174732884729</v>
       </c>
       <c r="N326">
-        <v>92.49655905062698</v>
+        <v>92.50023850677903</v>
       </c>
       <c r="O326">
         <v>89.37013344697753</v>
@@ -18815,7 +18815,7 @@
         <v>89.87174732884729</v>
       </c>
       <c r="N327">
-        <v>92.49655905062698</v>
+        <v>92.50023850677903</v>
       </c>
       <c r="O327">
         <v>89.37013344697753</v>
@@ -18871,7 +18871,7 @@
         <v>89.87174732884729</v>
       </c>
       <c r="N328">
-        <v>92.49655905062698</v>
+        <v>92.50023850677903</v>
       </c>
       <c r="O328">
         <v>89.37013344697753</v>
@@ -18883,7 +18883,7 @@
         <v>26</v>
       </c>
       <c r="S328">
-        <v>-0.003681425407009442</v>
+        <v>-1.969254959099942E-06</v>
       </c>
     </row>
     <row r="329" spans="1:19">
@@ -18927,7 +18927,7 @@
         <v>89.87174732884729</v>
       </c>
       <c r="N329">
-        <v>92.49655905062698</v>
+        <v>92.50023850677903</v>
       </c>
       <c r="O329">
         <v>89.37013344697753</v>
@@ -18962,13 +18962,13 @@
         <v>46</v>
       </c>
       <c r="G330" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H330" t="b">
         <v>0</v>
       </c>
       <c r="I330" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J330" t="b">
         <v>1</v>
@@ -18983,7 +18983,7 @@
         <v>56.48489093186536</v>
       </c>
       <c r="N330">
-        <v>56.81048504636033</v>
+        <v>53.23482090182604</v>
       </c>
       <c r="O330">
         <v>53.74844900886458</v>
@@ -19018,13 +19018,13 @@
         <v>46</v>
       </c>
       <c r="G331" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H331" t="b">
         <v>0</v>
       </c>
       <c r="I331" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J331" t="b">
         <v>1</v>
@@ -19039,7 +19039,7 @@
         <v>56.48489093186536</v>
       </c>
       <c r="N331">
-        <v>56.81048504636033</v>
+        <v>53.23482090182604</v>
       </c>
       <c r="O331">
         <v>53.74844900886458</v>
@@ -19074,13 +19074,13 @@
         <v>46</v>
       </c>
       <c r="G332" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H332" t="b">
         <v>0</v>
       </c>
       <c r="I332" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J332" t="b">
         <v>1</v>
@@ -19095,7 +19095,7 @@
         <v>56.48489093186536</v>
       </c>
       <c r="N332">
-        <v>56.81048504636033</v>
+        <v>53.23482090182604</v>
       </c>
       <c r="O332">
         <v>53.74844900886458</v>
@@ -19107,7 +19107,7 @@
         <v>26</v>
       </c>
       <c r="S332">
-        <v>0.005345511122456514</v>
+        <v>-3.57031863341184</v>
       </c>
     </row>
     <row r="333" spans="1:19">
@@ -19130,13 +19130,13 @@
         <v>46</v>
       </c>
       <c r="G333" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H333" t="b">
         <v>0</v>
       </c>
       <c r="I333" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J333" t="b">
         <v>1</v>
@@ -19151,7 +19151,7 @@
         <v>56.48489093186536</v>
       </c>
       <c r="N333">
-        <v>56.81048504636033</v>
+        <v>53.23482090182604</v>
       </c>
       <c r="O333">
         <v>53.74844900886458</v>
@@ -19186,19 +19186,19 @@
         <v>46</v>
       </c>
       <c r="G334" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H334" t="b">
         <v>0</v>
       </c>
       <c r="I334" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J334" t="b">
         <v>1</v>
       </c>
       <c r="K334">
-        <v>61.83283312951136</v>
+        <v>61.6228045760042</v>
       </c>
       <c r="L334">
         <v>94.29505212642727</v>
@@ -19207,7 +19207,7 @@
         <v>90.36761926846003</v>
       </c>
       <c r="N334">
-        <v>62.32157982437181</v>
+        <v>94.66242032680918</v>
       </c>
       <c r="O334">
         <v>94.7901531154163</v>
@@ -19219,7 +19219,7 @@
         <v>24</v>
       </c>
       <c r="S334">
-        <v>32.4622189969159</v>
+        <v>32.67224755042307</v>
       </c>
     </row>
     <row r="335" spans="1:19">
@@ -19242,19 +19242,19 @@
         <v>46</v>
       </c>
       <c r="G335" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H335" t="b">
         <v>0</v>
       </c>
       <c r="I335" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J335" t="b">
         <v>1</v>
       </c>
       <c r="K335">
-        <v>61.83283312951136</v>
+        <v>61.6228045760042</v>
       </c>
       <c r="L335">
         <v>94.29505212642727</v>
@@ -19263,7 +19263,7 @@
         <v>90.36761926846003</v>
       </c>
       <c r="N335">
-        <v>62.32157982437181</v>
+        <v>94.66242032680918</v>
       </c>
       <c r="O335">
         <v>94.7901531154163</v>
@@ -19275,7 +19275,7 @@
         <v>25</v>
       </c>
       <c r="S335">
-        <v>28.53478613894866</v>
+        <v>28.74481469245583</v>
       </c>
     </row>
     <row r="336" spans="1:19">
@@ -19298,19 +19298,19 @@
         <v>46</v>
       </c>
       <c r="G336" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H336" t="b">
         <v>0</v>
       </c>
       <c r="I336" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J336" t="b">
         <v>1</v>
       </c>
       <c r="K336">
-        <v>61.83283312951136</v>
+        <v>61.6228045760042</v>
       </c>
       <c r="L336">
         <v>94.29505212642727</v>
@@ -19319,7 +19319,7 @@
         <v>90.36761926846003</v>
       </c>
       <c r="N336">
-        <v>62.32157982437181</v>
+        <v>94.66242032680918</v>
       </c>
       <c r="O336">
         <v>94.7901531154163</v>
@@ -19331,7 +19331,7 @@
         <v>26</v>
       </c>
       <c r="S336">
-        <v>0.4887466948604424</v>
+        <v>33.03961575080498</v>
       </c>
     </row>
     <row r="337" spans="1:19">
@@ -19354,19 +19354,19 @@
         <v>46</v>
       </c>
       <c r="G337" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H337" t="b">
         <v>0</v>
       </c>
       <c r="I337" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J337" t="b">
         <v>1</v>
       </c>
       <c r="K337">
-        <v>61.83283312951136</v>
+        <v>61.6228045760042</v>
       </c>
       <c r="L337">
         <v>94.29505212642727</v>
@@ -19375,7 +19375,7 @@
         <v>90.36761926846003</v>
       </c>
       <c r="N337">
-        <v>62.32157982437181</v>
+        <v>94.66242032680918</v>
       </c>
       <c r="O337">
         <v>94.7901531154163</v>
@@ -19387,7 +19387,7 @@
         <v>27</v>
       </c>
       <c r="S337">
-        <v>32.95731998590495</v>
+        <v>33.16734853941211</v>
       </c>
     </row>
     <row r="338" spans="1:19">
@@ -19431,7 +19431,7 @@
         <v>20.26581866993463</v>
       </c>
       <c r="N338">
-        <v>19.78924651381285</v>
+        <v>19.78925504151854</v>
       </c>
       <c r="O338">
         <v>19.78925504151844</v>
@@ -19487,7 +19487,7 @@
         <v>20.26581866993463</v>
       </c>
       <c r="N339">
-        <v>19.78924651381285</v>
+        <v>19.78925504151854</v>
       </c>
       <c r="O339">
         <v>19.78925504151844</v>
@@ -19543,7 +19543,7 @@
         <v>20.26581866993463</v>
       </c>
       <c r="N340">
-        <v>19.78924651381285</v>
+        <v>19.78925504151854</v>
       </c>
       <c r="O340">
         <v>19.78925504151844</v>
@@ -19555,7 +19555,7 @@
         <v>26</v>
       </c>
       <c r="S340">
-        <v>-8.527705555594345E-06</v>
+        <v>1.332267629550188E-13</v>
       </c>
     </row>
     <row r="341" spans="1:19">
@@ -19599,7 +19599,7 @@
         <v>20.26581866993463</v>
       </c>
       <c r="N341">
-        <v>19.78924651381285</v>
+        <v>19.78925504151854</v>
       </c>
       <c r="O341">
         <v>19.78925504151844</v>
@@ -19655,7 +19655,7 @@
         <v>28.96056268438987</v>
       </c>
       <c r="N342">
-        <v>29.12343582453531</v>
+        <v>29.12342358088592</v>
       </c>
       <c r="O342">
         <v>29.12342358088539</v>
@@ -19711,7 +19711,7 @@
         <v>28.96056268438987</v>
       </c>
       <c r="N343">
-        <v>29.12343582453531</v>
+        <v>29.12342358088592</v>
       </c>
       <c r="O343">
         <v>29.12342358088539</v>
@@ -19767,7 +19767,7 @@
         <v>28.96056268438987</v>
       </c>
       <c r="N344">
-        <v>29.12343582453531</v>
+        <v>29.12342358088592</v>
       </c>
       <c r="O344">
         <v>29.12342358088539</v>
@@ -19779,7 +19779,7 @@
         <v>26</v>
       </c>
       <c r="S344">
-        <v>1.224364997720606E-05</v>
+        <v>5.828670879282072E-13</v>
       </c>
     </row>
     <row r="345" spans="1:19">
@@ -19823,7 +19823,7 @@
         <v>28.96056268438987</v>
       </c>
       <c r="N345">
-        <v>29.12343582453531</v>
+        <v>29.12342358088592</v>
       </c>
       <c r="O345">
         <v>29.12342358088539</v>
@@ -19879,7 +19879,7 @@
         <v>49.14854198657082</v>
       </c>
       <c r="N346">
-        <v>60.91535029185478</v>
+        <v>60.91538488022691</v>
       </c>
       <c r="O346">
         <v>60.91538488022658</v>
@@ -19935,7 +19935,7 @@
         <v>49.14854198657082</v>
       </c>
       <c r="N347">
-        <v>60.91535029185478</v>
+        <v>60.91538488022691</v>
       </c>
       <c r="O347">
         <v>60.91538488022658</v>
@@ -19991,7 +19991,7 @@
         <v>49.14854198657082</v>
       </c>
       <c r="N348">
-        <v>60.91535029185478</v>
+        <v>60.91538488022691</v>
       </c>
       <c r="O348">
         <v>60.91538488022658</v>
@@ -20003,7 +20003,7 @@
         <v>26</v>
       </c>
       <c r="S348">
-        <v>-3.458837184444619E-05</v>
+        <v>2.886579864025407E-13</v>
       </c>
     </row>
     <row r="349" spans="1:19">
@@ -20047,7 +20047,7 @@
         <v>49.14854198657082</v>
       </c>
       <c r="N349">
-        <v>60.91535029185478</v>
+        <v>60.91538488022691</v>
       </c>
       <c r="O349">
         <v>60.91538488022658</v>
@@ -20103,7 +20103,7 @@
         <v>22.44485917007791</v>
       </c>
       <c r="N350">
-        <v>23.77362781109571</v>
+        <v>23.77362873790559</v>
       </c>
       <c r="O350">
         <v>23.77362873790571</v>
@@ -20159,7 +20159,7 @@
         <v>22.44485917007791</v>
       </c>
       <c r="N351">
-        <v>23.77362781109571</v>
+        <v>23.77362873790559</v>
       </c>
       <c r="O351">
         <v>23.77362873790571</v>
@@ -20215,7 +20215,7 @@
         <v>22.44485917007791</v>
       </c>
       <c r="N352">
-        <v>23.77362781109571</v>
+        <v>23.77362873790559</v>
       </c>
       <c r="O352">
         <v>23.77362873790571</v>
@@ -20227,7 +20227,7 @@
         <v>26</v>
       </c>
       <c r="S352">
-        <v>-9.268099454562417E-07</v>
+        <v>-6.661338147750939E-14</v>
       </c>
     </row>
     <row r="353" spans="1:19">
@@ -20271,7 +20271,7 @@
         <v>22.44485917007791</v>
       </c>
       <c r="N353">
-        <v>23.77362781109571</v>
+        <v>23.77362873790559</v>
       </c>
       <c r="O353">
         <v>23.77362873790571</v>
@@ -20327,7 +20327,7 @@
         <v>91.70603958663986</v>
       </c>
       <c r="N354">
-        <v>86.61759533781009</v>
+        <v>86.6175911243575</v>
       </c>
       <c r="O354">
         <v>91.00299874324041</v>
@@ -20383,7 +20383,7 @@
         <v>91.70603958663986</v>
       </c>
       <c r="N355">
-        <v>86.61759533781009</v>
+        <v>86.6175911243575</v>
       </c>
       <c r="O355">
         <v>91.00299874324041</v>
@@ -20439,7 +20439,7 @@
         <v>91.70603958663986</v>
       </c>
       <c r="N356">
-        <v>86.61759533781009</v>
+        <v>86.6175911243575</v>
       </c>
       <c r="O356">
         <v>91.00299874324041</v>
@@ -20451,7 +20451,7 @@
         <v>26</v>
       </c>
       <c r="S356">
-        <v>4.213452531320883E-06</v>
+        <v>-4.440892098500626E-14</v>
       </c>
     </row>
     <row r="357" spans="1:19">
@@ -20495,7 +20495,7 @@
         <v>91.70603958663986</v>
       </c>
       <c r="N357">
-        <v>86.61759533781009</v>
+        <v>86.6175911243575</v>
       </c>
       <c r="O357">
         <v>91.00299874324041</v>
@@ -20530,13 +20530,13 @@
         <v>46</v>
       </c>
       <c r="G358" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H358" t="b">
         <v>0</v>
       </c>
       <c r="I358" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J358" t="b">
         <v>1</v>
@@ -20551,7 +20551,7 @@
         <v>61.86336116134829</v>
       </c>
       <c r="N358">
-        <v>61.01690685229704</v>
+        <v>60.96897159585668</v>
       </c>
       <c r="O358">
         <v>60.90792656592394</v>
@@ -20586,13 +20586,13 @@
         <v>46</v>
       </c>
       <c r="G359" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H359" t="b">
         <v>0</v>
       </c>
       <c r="I359" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J359" t="b">
         <v>1</v>
@@ -20607,7 +20607,7 @@
         <v>61.86336116134829</v>
       </c>
       <c r="N359">
-        <v>61.01690685229704</v>
+        <v>60.96897159585668</v>
       </c>
       <c r="O359">
         <v>60.90792656592394</v>
@@ -20642,13 +20642,13 @@
         <v>46</v>
       </c>
       <c r="G360" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H360" t="b">
         <v>0</v>
       </c>
       <c r="I360" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J360" t="b">
         <v>1</v>
@@ -20663,7 +20663,7 @@
         <v>61.86336116134829</v>
       </c>
       <c r="N360">
-        <v>61.01690685229704</v>
+        <v>60.96897159585668</v>
       </c>
       <c r="O360">
         <v>60.90792656592394</v>
@@ -20675,7 +20675,7 @@
         <v>26</v>
       </c>
       <c r="S360">
-        <v>9.992007221626409E-14</v>
+        <v>-0.04793525644025687</v>
       </c>
     </row>
     <row r="361" spans="1:19">
@@ -20698,13 +20698,13 @@
         <v>46</v>
       </c>
       <c r="G361" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H361" t="b">
         <v>0</v>
       </c>
       <c r="I361" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J361" t="b">
         <v>1</v>
@@ -20719,7 +20719,7 @@
         <v>61.86336116134829</v>
       </c>
       <c r="N361">
-        <v>61.01690685229704</v>
+        <v>60.96897159585668</v>
       </c>
       <c r="O361">
         <v>60.90792656592394</v>
@@ -20754,7 +20754,7 @@
         <v>45</v>
       </c>
       <c r="G362" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H362" t="b">
         <v>0</v>
@@ -20775,7 +20775,7 @@
         <v>52.0486362227494</v>
       </c>
       <c r="N362">
-        <v>51.58328680758268</v>
+        <v>53.11833476492082</v>
       </c>
       <c r="O362">
         <v>51.64851811913296</v>
@@ -20810,7 +20810,7 @@
         <v>45</v>
       </c>
       <c r="G363" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H363" t="b">
         <v>0</v>
@@ -20831,7 +20831,7 @@
         <v>52.0486362227494</v>
       </c>
       <c r="N363">
-        <v>51.58328680758268</v>
+        <v>53.11833476492082</v>
       </c>
       <c r="O363">
         <v>51.64851811913296</v>
@@ -20866,7 +20866,7 @@
         <v>45</v>
       </c>
       <c r="G364" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H364" t="b">
         <v>0</v>
@@ -20887,7 +20887,7 @@
         <v>52.0486362227494</v>
       </c>
       <c r="N364">
-        <v>51.58328680758268</v>
+        <v>53.11833476492082</v>
       </c>
       <c r="O364">
         <v>51.64851811913296</v>
@@ -20899,7 +20899,7 @@
         <v>26</v>
       </c>
       <c r="S364">
-        <v>-1.581495912006403E-06</v>
+        <v>1.535046375842231</v>
       </c>
     </row>
     <row r="365" spans="1:19">
@@ -20922,7 +20922,7 @@
         <v>45</v>
       </c>
       <c r="G365" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H365" t="b">
         <v>0</v>
@@ -20943,7 +20943,7 @@
         <v>52.0486362227494</v>
       </c>
       <c r="N365">
-        <v>51.58328680758268</v>
+        <v>53.11833476492082</v>
       </c>
       <c r="O365">
         <v>51.64851811913296</v>
@@ -20999,7 +20999,7 @@
         <v>93.97256936242141</v>
       </c>
       <c r="N366">
-        <v>89.30448406446422</v>
+        <v>89.30448723235351</v>
       </c>
       <c r="O366">
         <v>92.02012063880795</v>
@@ -21055,7 +21055,7 @@
         <v>93.97256936242141</v>
       </c>
       <c r="N367">
-        <v>89.30448406446422</v>
+        <v>89.30448723235351</v>
       </c>
       <c r="O367">
         <v>92.02012063880795</v>
@@ -21111,7 +21111,7 @@
         <v>93.97256936242141</v>
       </c>
       <c r="N368">
-        <v>89.30448406446422</v>
+        <v>89.30448723235351</v>
       </c>
       <c r="O368">
         <v>92.02012063880795</v>
@@ -21123,7 +21123,7 @@
         <v>26</v>
       </c>
       <c r="S368">
-        <v>-3.167889339739105E-06</v>
+        <v>-5.551115123125783E-14</v>
       </c>
     </row>
     <row r="369" spans="1:19">
@@ -21167,7 +21167,7 @@
         <v>93.97256936242141</v>
       </c>
       <c r="N369">
-        <v>89.30448406446422</v>
+        <v>89.30448723235351</v>
       </c>
       <c r="O369">
         <v>92.02012063880795</v>
@@ -21223,7 +21223,7 @@
         <v>90.54993362185887</v>
       </c>
       <c r="N370">
-        <v>92.88968375251611</v>
+        <v>92.8896869588861</v>
       </c>
       <c r="O370">
         <v>89.56120922251529</v>
@@ -21279,7 +21279,7 @@
         <v>90.54993362185887</v>
       </c>
       <c r="N371">
-        <v>92.88968375251611</v>
+        <v>92.8896869588861</v>
       </c>
       <c r="O371">
         <v>89.56120922251529</v>
@@ -21335,7 +21335,7 @@
         <v>90.54993362185887</v>
       </c>
       <c r="N372">
-        <v>92.88968375251611</v>
+        <v>92.8896869588861</v>
       </c>
       <c r="O372">
         <v>89.56120922251529</v>
@@ -21347,7 +21347,7 @@
         <v>26</v>
       </c>
       <c r="S372">
-        <v>-3.206370080555132E-06</v>
+        <v>-8.881784197001252E-14</v>
       </c>
     </row>
     <row r="373" spans="1:19">
@@ -21391,7 +21391,7 @@
         <v>90.54993362185887</v>
       </c>
       <c r="N373">
-        <v>92.88968375251611</v>
+        <v>92.8896869588861</v>
       </c>
       <c r="O373">
         <v>89.56120922251529</v>
@@ -21426,13 +21426,13 @@
         <v>46</v>
       </c>
       <c r="G374" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H374" t="b">
         <v>0</v>
       </c>
       <c r="I374" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J374" t="b">
         <v>1</v>
@@ -21447,7 +21447,7 @@
         <v>66.32389529839756</v>
       </c>
       <c r="N374">
-        <v>68.08470970859113</v>
+        <v>64.43326931382676</v>
       </c>
       <c r="O374">
         <v>65.01957153073924</v>
@@ -21482,13 +21482,13 @@
         <v>46</v>
       </c>
       <c r="G375" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H375" t="b">
         <v>0</v>
       </c>
       <c r="I375" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J375" t="b">
         <v>1</v>
@@ -21503,7 +21503,7 @@
         <v>66.32389529839756</v>
       </c>
       <c r="N375">
-        <v>68.08470970859113</v>
+        <v>64.43326931382676</v>
       </c>
       <c r="O375">
         <v>65.01957153073924</v>
@@ -21538,13 +21538,13 @@
         <v>46</v>
       </c>
       <c r="G376" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H376" t="b">
         <v>0</v>
       </c>
       <c r="I376" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J376" t="b">
         <v>1</v>
@@ -21559,7 +21559,7 @@
         <v>66.32389529839756</v>
       </c>
       <c r="N376">
-        <v>68.08470970859113</v>
+        <v>64.43326931382676</v>
       </c>
       <c r="O376">
         <v>65.01957153073924</v>
@@ -21571,7 +21571,7 @@
         <v>26</v>
       </c>
       <c r="S376">
-        <v>-1.165074237086117E-06</v>
+        <v>-3.651441559838609</v>
       </c>
     </row>
     <row r="377" spans="1:19">
@@ -21594,13 +21594,13 @@
         <v>46</v>
       </c>
       <c r="G377" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H377" t="b">
         <v>0</v>
       </c>
       <c r="I377" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J377" t="b">
         <v>1</v>
@@ -21615,7 +21615,7 @@
         <v>66.32389529839756</v>
       </c>
       <c r="N377">
-        <v>68.08470970859113</v>
+        <v>64.43326931382676</v>
       </c>
       <c r="O377">
         <v>65.01957153073924</v>
@@ -21650,7 +21650,7 @@
         <v>45</v>
       </c>
       <c r="G378" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H378" t="b">
         <v>0</v>
@@ -21662,7 +21662,7 @@
         <v>0</v>
       </c>
       <c r="K378">
-        <v>57.1867220532585</v>
+        <v>57.0310306987091</v>
       </c>
       <c r="L378">
         <v>15.23428499612493</v>
@@ -21671,7 +21671,7 @@
         <v>7.1175865533443</v>
       </c>
       <c r="N378">
-        <v>57.18661836637945</v>
+        <v>14.80223927521161</v>
       </c>
       <c r="O378">
         <v>14.71857655337873</v>
@@ -21683,7 +21683,7 @@
         <v>24</v>
       </c>
       <c r="S378">
-        <v>-41.95243705713357</v>
+        <v>-41.79674570258417</v>
       </c>
     </row>
     <row r="379" spans="1:19">
@@ -21706,7 +21706,7 @@
         <v>45</v>
       </c>
       <c r="G379" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H379" t="b">
         <v>0</v>
@@ -21718,7 +21718,7 @@
         <v>0</v>
       </c>
       <c r="K379">
-        <v>57.1867220532585</v>
+        <v>57.0310306987091</v>
       </c>
       <c r="L379">
         <v>15.23428499612493</v>
@@ -21727,7 +21727,7 @@
         <v>7.1175865533443</v>
       </c>
       <c r="N379">
-        <v>57.18661836637945</v>
+        <v>14.80223927521161</v>
       </c>
       <c r="O379">
         <v>14.71857655337873</v>
@@ -21739,7 +21739,7 @@
         <v>25</v>
       </c>
       <c r="S379">
-        <v>-50.0691354999142</v>
+        <v>-49.91344414536479</v>
       </c>
     </row>
     <row r="380" spans="1:19">
@@ -21762,7 +21762,7 @@
         <v>45</v>
       </c>
       <c r="G380" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H380" t="b">
         <v>0</v>
@@ -21774,7 +21774,7 @@
         <v>0</v>
       </c>
       <c r="K380">
-        <v>57.1867220532585</v>
+        <v>57.0310306987091</v>
       </c>
       <c r="L380">
         <v>15.23428499612493</v>
@@ -21783,7 +21783,7 @@
         <v>7.1175865533443</v>
       </c>
       <c r="N380">
-        <v>57.18661836637945</v>
+        <v>14.80223927521161</v>
       </c>
       <c r="O380">
         <v>14.71857655337873</v>
@@ -21795,7 +21795,7 @@
         <v>26</v>
       </c>
       <c r="S380">
-        <v>-0.0001036868790493806</v>
+        <v>-42.22879142349748</v>
       </c>
     </row>
     <row r="381" spans="1:19">
@@ -21818,7 +21818,7 @@
         <v>45</v>
       </c>
       <c r="G381" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H381" t="b">
         <v>0</v>
@@ -21830,7 +21830,7 @@
         <v>0</v>
       </c>
       <c r="K381">
-        <v>57.1867220532585</v>
+        <v>57.0310306987091</v>
       </c>
       <c r="L381">
         <v>15.23428499612493</v>
@@ -21839,7 +21839,7 @@
         <v>7.1175865533443</v>
       </c>
       <c r="N381">
-        <v>57.18661836637945</v>
+        <v>14.80223927521161</v>
       </c>
       <c r="O381">
         <v>14.71857655337873</v>
@@ -21851,7 +21851,7 @@
         <v>27</v>
       </c>
       <c r="S381">
-        <v>-42.46814549987977</v>
+        <v>-42.31245414533036</v>
       </c>
     </row>
   </sheetData>

--- a/tables_and_figures/input_tables/national_errors.xlsx
+++ b/tables_and_figures/input_tables/national_errors.xlsx
@@ -2398,7 +2398,7 @@
         <v>1</v>
       </c>
       <c r="K34">
-        <v>62.08476673915371</v>
+        <v>58.53764797567101</v>
       </c>
       <c r="L34">
         <v>10.21307356029052</v>
@@ -2419,7 +2419,7 @@
         <v>24</v>
       </c>
       <c r="S34">
-        <v>-51.87169317886319</v>
+        <v>-48.32457441538048</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -2454,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="K35">
-        <v>62.08476673915371</v>
+        <v>58.53764797567101</v>
       </c>
       <c r="L35">
         <v>10.21307356029052</v>
@@ -2475,7 +2475,7 @@
         <v>25</v>
       </c>
       <c r="S35">
-        <v>-48.37189542905355</v>
+        <v>-44.82477666557084</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -2510,7 +2510,7 @@
         <v>1</v>
       </c>
       <c r="K36">
-        <v>62.08476673915371</v>
+        <v>58.53764797567101</v>
       </c>
       <c r="L36">
         <v>10.21307356029052</v>
@@ -2531,7 +2531,7 @@
         <v>26</v>
       </c>
       <c r="S36">
-        <v>-48.75005182672324</v>
+        <v>-45.20293306324054</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -2566,7 +2566,7 @@
         <v>1</v>
       </c>
       <c r="K37">
-        <v>62.08476673915371</v>
+        <v>58.53764797567101</v>
       </c>
       <c r="L37">
         <v>10.21307356029052</v>
@@ -2587,7 +2587,7 @@
         <v>27</v>
       </c>
       <c r="S37">
-        <v>-48.68608362552613</v>
+        <v>-45.13896486204343</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -4638,7 +4638,7 @@
         <v>0</v>
       </c>
       <c r="K74">
-        <v>57.3909499335277</v>
+        <v>62.6433899163336</v>
       </c>
       <c r="L74">
         <v>89.80584340279077</v>
@@ -4659,7 +4659,7 @@
         <v>24</v>
       </c>
       <c r="S74">
-        <v>32.41489346926306</v>
+        <v>27.16245348645716</v>
       </c>
     </row>
     <row r="75" spans="1:19">
@@ -4694,7 +4694,7 @@
         <v>0</v>
       </c>
       <c r="K75">
-        <v>57.3909499335277</v>
+        <v>62.6433899163336</v>
       </c>
       <c r="L75">
         <v>89.80584340279077</v>
@@ -4715,7 +4715,7 @@
         <v>25</v>
       </c>
       <c r="S75">
-        <v>27.62128691766935</v>
+        <v>22.36884693486345</v>
       </c>
     </row>
     <row r="76" spans="1:19">
@@ -4750,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="K76">
-        <v>57.3909499335277</v>
+        <v>62.6433899163336</v>
       </c>
       <c r="L76">
         <v>89.80584340279077</v>
@@ -4771,7 +4771,7 @@
         <v>26</v>
       </c>
       <c r="S76">
-        <v>31.26779481350348</v>
+        <v>26.01535483069758</v>
       </c>
     </row>
     <row r="77" spans="1:19">
@@ -4806,7 +4806,7 @@
         <v>0</v>
       </c>
       <c r="K77">
-        <v>57.3909499335277</v>
+        <v>62.6433899163336</v>
       </c>
       <c r="L77">
         <v>89.80584340279077</v>
@@ -4827,7 +4827,7 @@
         <v>27</v>
       </c>
       <c r="S77">
-        <v>31.21755793806243</v>
+        <v>25.96511795525653</v>
       </c>
     </row>
     <row r="78" spans="1:19">
@@ -7102,7 +7102,7 @@
         <v>0</v>
       </c>
       <c r="K118">
-        <v>61.48758237299869</v>
+        <v>57.85387248332849</v>
       </c>
       <c r="L118">
         <v>15.85204755614267</v>
@@ -7123,7 +7123,7 @@
         <v>24</v>
       </c>
       <c r="S118">
-        <v>-45.63553481685603</v>
+        <v>-42.00182492718583</v>
       </c>
     </row>
     <row r="119" spans="1:19">
@@ -7158,7 +7158,7 @@
         <v>0</v>
       </c>
       <c r="K119">
-        <v>61.48758237299869</v>
+        <v>57.85387248332849</v>
       </c>
       <c r="L119">
         <v>15.85204755614267</v>
@@ -7179,7 +7179,7 @@
         <v>25</v>
       </c>
       <c r="S119">
-        <v>-33.85444908186454</v>
+        <v>-30.22073919219433</v>
       </c>
     </row>
     <row r="120" spans="1:19">
@@ -7214,7 +7214,7 @@
         <v>0</v>
       </c>
       <c r="K120">
-        <v>61.48758237299869</v>
+        <v>57.85387248332849</v>
       </c>
       <c r="L120">
         <v>15.85204755614267</v>
@@ -7235,7 +7235,7 @@
         <v>26</v>
       </c>
       <c r="S120">
-        <v>-35.87001168407564</v>
+        <v>-32.23630179440543</v>
       </c>
     </row>
     <row r="121" spans="1:19">
@@ -7270,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="K121">
-        <v>61.48758237299869</v>
+        <v>57.85387248332849</v>
       </c>
       <c r="L121">
         <v>15.85204755614267</v>
@@ -7291,7 +7291,7 @@
         <v>27</v>
       </c>
       <c r="S121">
-        <v>-35.11721323032864</v>
+        <v>-31.48350334065845</v>
       </c>
     </row>
     <row r="122" spans="1:19">
@@ -9566,7 +9566,7 @@
         <v>0</v>
       </c>
       <c r="K162">
-        <v>53.9917012472936</v>
+        <v>58.9487860548799</v>
       </c>
       <c r="L162">
         <v>93.32799321490836</v>
@@ -9587,7 +9587,7 @@
         <v>24</v>
       </c>
       <c r="S162">
-        <v>39.33629196761476</v>
+        <v>34.37920716002846</v>
       </c>
     </row>
     <row r="163" spans="1:19">
@@ -9622,7 +9622,7 @@
         <v>0</v>
       </c>
       <c r="K163">
-        <v>53.9917012472936</v>
+        <v>58.9487860548799</v>
       </c>
       <c r="L163">
         <v>93.32799321490836</v>
@@ -9643,7 +9643,7 @@
         <v>25</v>
       </c>
       <c r="S163">
-        <v>40.93257833336629</v>
+        <v>35.97549352577999</v>
       </c>
     </row>
     <row r="164" spans="1:19">
@@ -9678,7 +9678,7 @@
         <v>0</v>
       </c>
       <c r="K164">
-        <v>53.9917012472936</v>
+        <v>58.9487860548799</v>
       </c>
       <c r="L164">
         <v>93.32799321490836</v>
@@ -9699,7 +9699,7 @@
         <v>26</v>
       </c>
       <c r="S164">
-        <v>36.87804756160919</v>
+        <v>31.9209627540229</v>
       </c>
     </row>
     <row r="165" spans="1:19">
@@ -9734,7 +9734,7 @@
         <v>0</v>
       </c>
       <c r="K165">
-        <v>53.9917012472936</v>
+        <v>58.9487860548799</v>
       </c>
       <c r="L165">
         <v>93.32799321490836</v>
@@ -9755,7 +9755,7 @@
         <v>27</v>
       </c>
       <c r="S165">
-        <v>36.82072060467674</v>
+        <v>31.86363579709044</v>
       </c>
     </row>
     <row r="166" spans="1:19">
@@ -12030,7 +12030,7 @@
         <v>1</v>
       </c>
       <c r="K206">
-        <v>66.13023562229581</v>
+        <v>63.06375972137231</v>
       </c>
       <c r="L206">
         <v>20.45869883040936</v>
@@ -12051,7 +12051,7 @@
         <v>24</v>
       </c>
       <c r="S206">
-        <v>-45.67153679188645</v>
+        <v>-42.60506089096295</v>
       </c>
     </row>
     <row r="207" spans="1:19">
@@ -12086,7 +12086,7 @@
         <v>1</v>
       </c>
       <c r="K207">
-        <v>66.13023562229581</v>
+        <v>63.06375972137231</v>
       </c>
       <c r="L207">
         <v>20.45869883040936</v>
@@ -12107,7 +12107,7 @@
         <v>25</v>
       </c>
       <c r="S207">
-        <v>-50.05777870600128</v>
+        <v>-46.99130280507777</v>
       </c>
     </row>
     <row r="208" spans="1:19">
@@ -12142,7 +12142,7 @@
         <v>1</v>
       </c>
       <c r="K208">
-        <v>66.13023562229581</v>
+        <v>63.06375972137231</v>
       </c>
       <c r="L208">
         <v>20.45869883040936</v>
@@ -12163,7 +12163,7 @@
         <v>26</v>
       </c>
       <c r="S208">
-        <v>-42.68873696686224</v>
+        <v>-39.62226106593874</v>
       </c>
     </row>
     <row r="209" spans="1:19">
@@ -12198,7 +12198,7 @@
         <v>1</v>
       </c>
       <c r="K209">
-        <v>66.13023562229581</v>
+        <v>63.06375972137231</v>
       </c>
       <c r="L209">
         <v>20.45869883040936</v>
@@ -12219,7 +12219,7 @@
         <v>27</v>
       </c>
       <c r="S209">
-        <v>-42.84433159538177</v>
+        <v>-39.77785569445827</v>
       </c>
     </row>
     <row r="210" spans="1:19">
@@ -14494,7 +14494,7 @@
         <v>1</v>
       </c>
       <c r="K250">
-        <v>55.4603219525063</v>
+        <v>60.45977516590651</v>
       </c>
       <c r="L250">
         <v>92.41490820524366</v>
@@ -14515,7 +14515,7 @@
         <v>24</v>
       </c>
       <c r="S250">
-        <v>36.95458625273736</v>
+        <v>31.95513303933716</v>
       </c>
     </row>
     <row r="251" spans="1:19">
@@ -14550,7 +14550,7 @@
         <v>1</v>
       </c>
       <c r="K251">
-        <v>55.4603219525063</v>
+        <v>60.45977516590651</v>
       </c>
       <c r="L251">
         <v>92.41490820524366</v>
@@ -14571,7 +14571,7 @@
         <v>25</v>
       </c>
       <c r="S251">
-        <v>37.99923351866112</v>
+        <v>32.99978030526092</v>
       </c>
     </row>
     <row r="252" spans="1:19">
@@ -14606,7 +14606,7 @@
         <v>1</v>
       </c>
       <c r="K252">
-        <v>55.4603219525063</v>
+        <v>60.45977516590651</v>
       </c>
       <c r="L252">
         <v>92.41490820524366</v>
@@ -14627,7 +14627,7 @@
         <v>26</v>
       </c>
       <c r="S252">
-        <v>36.39698451075576</v>
+        <v>31.39753129735555</v>
       </c>
     </row>
     <row r="253" spans="1:19">
@@ -14662,7 +14662,7 @@
         <v>1</v>
       </c>
       <c r="K253">
-        <v>55.4603219525063</v>
+        <v>60.45977516590651</v>
       </c>
       <c r="L253">
         <v>92.41490820524366</v>
@@ -14683,7 +14683,7 @@
         <v>27</v>
       </c>
       <c r="S253">
-        <v>36.54701397840824</v>
+        <v>31.54756076500803</v>
       </c>
     </row>
     <row r="254" spans="1:19">
@@ -16716,7 +16716,7 @@
         <v>43</v>
       </c>
       <c r="E290" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F290" t="s">
         <v>46</v>
@@ -16734,19 +16734,19 @@
         <v>1</v>
       </c>
       <c r="K290">
-        <v>53.31034912579611</v>
+        <v>50.477072976542</v>
       </c>
       <c r="L290">
-        <v>11.78252784220314</v>
+        <v>88.21747215779686</v>
       </c>
       <c r="M290">
-        <v>16.02529247027256</v>
+        <v>83.97470752972744</v>
       </c>
       <c r="N290">
-        <v>11.48115825434971</v>
+        <v>88.51884174565029</v>
       </c>
       <c r="O290">
-        <v>11.76849713904182</v>
+        <v>88.23150286095819</v>
       </c>
       <c r="P290">
         <v>47859</v>
@@ -16755,7 +16755,7 @@
         <v>24</v>
       </c>
       <c r="S290">
-        <v>-41.52782128359297</v>
+        <v>37.74039918125486</v>
       </c>
     </row>
     <row r="291" spans="1:19">
@@ -16772,7 +16772,7 @@
         <v>43</v>
       </c>
       <c r="E291" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F291" t="s">
         <v>46</v>
@@ -16790,19 +16790,19 @@
         <v>1</v>
       </c>
       <c r="K291">
-        <v>53.31034912579611</v>
+        <v>50.477072976542</v>
       </c>
       <c r="L291">
-        <v>11.78252784220314</v>
+        <v>88.21747215779686</v>
       </c>
       <c r="M291">
-        <v>16.02529247027256</v>
+        <v>83.97470752972744</v>
       </c>
       <c r="N291">
-        <v>11.48115825434971</v>
+        <v>88.51884174565029</v>
       </c>
       <c r="O291">
-        <v>11.76849713904182</v>
+        <v>88.23150286095819</v>
       </c>
       <c r="P291">
         <v>47859</v>
@@ -16811,7 +16811,7 @@
         <v>25</v>
       </c>
       <c r="S291">
-        <v>-37.28505665552355</v>
+        <v>33.49763455318543</v>
       </c>
     </row>
     <row r="292" spans="1:19">
@@ -16828,7 +16828,7 @@
         <v>43</v>
       </c>
       <c r="E292" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F292" t="s">
         <v>46</v>
@@ -16846,19 +16846,19 @@
         <v>1</v>
       </c>
       <c r="K292">
-        <v>53.31034912579611</v>
+        <v>50.477072976542</v>
       </c>
       <c r="L292">
-        <v>11.78252784220314</v>
+        <v>88.21747215779686</v>
       </c>
       <c r="M292">
-        <v>16.02529247027256</v>
+        <v>83.97470752972744</v>
       </c>
       <c r="N292">
-        <v>11.48115825434971</v>
+        <v>88.51884174565029</v>
       </c>
       <c r="O292">
-        <v>11.76849713904182</v>
+        <v>88.23150286095819</v>
       </c>
       <c r="P292">
         <v>47859</v>
@@ -16867,7 +16867,7 @@
         <v>26</v>
       </c>
       <c r="S292">
-        <v>-41.8291908714464</v>
+        <v>38.04176876910829</v>
       </c>
     </row>
     <row r="293" spans="1:19">
@@ -16884,7 +16884,7 @@
         <v>43</v>
       </c>
       <c r="E293" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F293" t="s">
         <v>46</v>
@@ -16902,19 +16902,19 @@
         <v>1</v>
       </c>
       <c r="K293">
-        <v>53.31034912579611</v>
+        <v>50.477072976542</v>
       </c>
       <c r="L293">
-        <v>11.78252784220314</v>
+        <v>88.21747215779686</v>
       </c>
       <c r="M293">
-        <v>16.02529247027256</v>
+        <v>83.97470752972744</v>
       </c>
       <c r="N293">
-        <v>11.48115825434971</v>
+        <v>88.51884174565029</v>
       </c>
       <c r="O293">
-        <v>11.76849713904182</v>
+        <v>88.23150286095819</v>
       </c>
       <c r="P293">
         <v>47859</v>
@@ -16923,7 +16923,7 @@
         <v>27</v>
       </c>
       <c r="S293">
-        <v>-41.54185198675429</v>
+        <v>37.75442988441618</v>
       </c>
     </row>
     <row r="294" spans="1:19">
@@ -19198,7 +19198,7 @@
         <v>1</v>
       </c>
       <c r="K334">
-        <v>61.6228045760042</v>
+        <v>66.6184922456773</v>
       </c>
       <c r="L334">
         <v>94.29505212642727</v>
@@ -19219,7 +19219,7 @@
         <v>24</v>
       </c>
       <c r="S334">
-        <v>32.67224755042307</v>
+        <v>27.67655988074997</v>
       </c>
     </row>
     <row r="335" spans="1:19">
@@ -19254,7 +19254,7 @@
         <v>1</v>
       </c>
       <c r="K335">
-        <v>61.6228045760042</v>
+        <v>66.6184922456773</v>
       </c>
       <c r="L335">
         <v>94.29505212642727</v>
@@ -19275,7 +19275,7 @@
         <v>25</v>
       </c>
       <c r="S335">
-        <v>28.74481469245583</v>
+        <v>23.74912702278273</v>
       </c>
     </row>
     <row r="336" spans="1:19">
@@ -19310,7 +19310,7 @@
         <v>1</v>
       </c>
       <c r="K336">
-        <v>61.6228045760042</v>
+        <v>66.6184922456773</v>
       </c>
       <c r="L336">
         <v>94.29505212642727</v>
@@ -19331,7 +19331,7 @@
         <v>26</v>
       </c>
       <c r="S336">
-        <v>33.03961575080498</v>
+        <v>28.04392808113188</v>
       </c>
     </row>
     <row r="337" spans="1:19">
@@ -19366,7 +19366,7 @@
         <v>1</v>
       </c>
       <c r="K337">
-        <v>61.6228045760042</v>
+        <v>66.6184922456773</v>
       </c>
       <c r="L337">
         <v>94.29505212642727</v>
@@ -19387,7 +19387,7 @@
         <v>27</v>
       </c>
       <c r="S337">
-        <v>33.16734853941211</v>
+        <v>28.17166086973901</v>
       </c>
     </row>
     <row r="338" spans="1:19">
@@ -21662,7 +21662,7 @@
         <v>0</v>
       </c>
       <c r="K378">
-        <v>57.0310306987091</v>
+        <v>53.51486207226939</v>
       </c>
       <c r="L378">
         <v>15.23428499612493</v>
@@ -21683,7 +21683,7 @@
         <v>24</v>
       </c>
       <c r="S378">
-        <v>-41.79674570258417</v>
+        <v>-38.28057707614447</v>
       </c>
     </row>
     <row r="379" spans="1:19">
@@ -21718,7 +21718,7 @@
         <v>0</v>
       </c>
       <c r="K379">
-        <v>57.0310306987091</v>
+        <v>53.51486207226939</v>
       </c>
       <c r="L379">
         <v>15.23428499612493</v>
@@ -21739,7 +21739,7 @@
         <v>25</v>
       </c>
       <c r="S379">
-        <v>-49.91344414536479</v>
+        <v>-46.3972755189251</v>
       </c>
     </row>
     <row r="380" spans="1:19">
@@ -21774,7 +21774,7 @@
         <v>0</v>
       </c>
       <c r="K380">
-        <v>57.0310306987091</v>
+        <v>53.51486207226939</v>
       </c>
       <c r="L380">
         <v>15.23428499612493</v>
@@ -21795,7 +21795,7 @@
         <v>26</v>
       </c>
       <c r="S380">
-        <v>-42.22879142349748</v>
+        <v>-38.71262279705778</v>
       </c>
     </row>
     <row r="381" spans="1:19">
@@ -21830,7 +21830,7 @@
         <v>0</v>
       </c>
       <c r="K381">
-        <v>57.0310306987091</v>
+        <v>53.51486207226939</v>
       </c>
       <c r="L381">
         <v>15.23428499612493</v>
@@ -21851,7 +21851,7 @@
         <v>27</v>
       </c>
       <c r="S381">
-        <v>-42.31245414533036</v>
+        <v>-38.79628551889066</v>
       </c>
     </row>
   </sheetData>
